--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3724" uniqueCount="2486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="2490">
   <si>
     <t>code</t>
   </si>
@@ -5653,7 +5653,7 @@
     <t>DK-CVR-12006004</t>
   </si>
   <si>
-    <t>Dansk MissionrÃ¥ds Udviklingsafdeling</t>
+    <t>Center for Church-Based Development</t>
   </si>
   <si>
     <t>XI-GRID-grid.9829.a</t>
@@ -7360,6 +7360,12 @@
     <t>University of Cape Town</t>
   </si>
   <si>
+    <t>XI-IATI-KHF</t>
+  </si>
+  <si>
+    <t>King Hussein Foundation</t>
+  </si>
+  <si>
     <t>GB-CHC-1158838</t>
   </si>
   <si>
@@ -7460,6 +7466,12 @@
   </si>
   <si>
     <t>CGIAR</t>
+  </si>
+  <si>
+    <t>UG-RSB-197310</t>
+  </si>
+  <si>
+    <t>Financial Sector Deepening Uganda</t>
   </si>
   <si>
     <t>ZM-PCR-12015013762</t>
@@ -7803,7 +7815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1240"/>
+  <dimension ref="A1:G1242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21458,6 +21470,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1241" spans="1:4">
+      <c r="A1241" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4">
+      <c r="A1242" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="2490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3733" uniqueCount="2492">
   <si>
     <t>code</t>
   </si>
@@ -7484,6 +7484,12 @@
   </si>
   <si>
     <t>United Nations Development Coordination Office</t>
+  </si>
+  <si>
+    <t>US-EIN-042103594</t>
+  </si>
+  <si>
+    <t>Abdul Latif Jameel Poverty Action Lab at MIT</t>
   </si>
 </sst>
 </file>
@@ -7815,7 +7821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1242"/>
+  <dimension ref="A1:G1243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21492,6 +21498,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1243" spans="1:4">
+      <c r="A1243" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>2491</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3733" uniqueCount="2492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3739" uniqueCount="2496">
   <si>
     <t>code</t>
   </si>
@@ -6874,6 +6874,12 @@
     <t>African Parks Network</t>
   </si>
   <si>
+    <t>GB-COH-06581421</t>
+  </si>
+  <si>
+    <t>The Institute for Strategic Dialogue</t>
+  </si>
+  <si>
     <t>ML-NIF-055000335T</t>
   </si>
   <si>
@@ -6908,6 +6914,12 @@
   </si>
   <si>
     <t>Nature and Development Foundation</t>
+  </si>
+  <si>
+    <t>BD-NAB-2004</t>
+  </si>
+  <si>
+    <t>Centre for Injury Prevention and Research, Bangladesh (CIPRB)</t>
   </si>
   <si>
     <t>XI-BRIDGE-1812689272</t>
@@ -7821,7 +7833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1243"/>
+  <dimension ref="A1:G1245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21509,6 +21521,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1244" spans="1:4">
+      <c r="A1244" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4">
+      <c r="A1245" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3739" uniqueCount="2496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="2498">
   <si>
     <t>code</t>
   </si>
@@ -1484,6 +1484,12 @@
   </si>
   <si>
     <t>Amref Health Africa - UK</t>
+  </si>
+  <si>
+    <t>XI-IATI-CHSA</t>
+  </si>
+  <si>
+    <t>Association CHS Alliance</t>
   </si>
   <si>
     <t>NL-KVK-40535338</t>
@@ -7833,7 +7839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1245"/>
+  <dimension ref="A1:G1246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21543,6 +21549,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1246" spans="1:4">
+      <c r="A1246" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3742" uniqueCount="2498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3745" uniqueCount="2500">
   <si>
     <t>code</t>
   </si>
@@ -7478,6 +7478,12 @@
   </si>
   <si>
     <t>JoWomenomics</t>
+  </si>
+  <si>
+    <t>XI-GRID-grid.11835.3e</t>
+  </si>
+  <si>
+    <t>The University of Sheffield</t>
   </si>
   <si>
     <t>XM-DAC-47015</t>
@@ -7839,7 +7845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1246"/>
+  <dimension ref="A1:G1247"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21560,6 +21566,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1247" spans="1:4">
+      <c r="A1247" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3745" uniqueCount="2500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="2506">
   <si>
     <t>code</t>
   </si>
@@ -1342,6 +1342,12 @@
     <t>Lepra</t>
   </si>
   <si>
+    <t>JO-CCD-50544</t>
+  </si>
+  <si>
+    <t>Arab Reporters for Investigative Journalism</t>
+  </si>
+  <si>
     <t>NL-KVK-41188664</t>
   </si>
   <si>
@@ -5554,6 +5560,12 @@
     <t>Deloitte Touche Tohmatsu India LLP</t>
   </si>
   <si>
+    <t>UG-NGO-1406</t>
+  </si>
+  <si>
+    <t>DefendDefenders</t>
+  </si>
+  <si>
     <t>KE-NCB-2180511703310709</t>
   </si>
   <si>
@@ -7382,6 +7394,12 @@
   </si>
   <si>
     <t>King Hussein Foundation</t>
+  </si>
+  <si>
+    <t>GB-COH-04465125</t>
+  </si>
+  <si>
+    <t>Imperial College of Science, Technology and Medicine</t>
   </si>
   <si>
     <t>GB-CHC-1158838</t>
@@ -7845,7 +7863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1247"/>
+  <dimension ref="A1:G1250"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21577,6 +21595,39 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1248" spans="1:4">
+      <c r="A1248" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4">
+      <c r="A1249" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4">
+      <c r="A1250" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="2506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3757" uniqueCount="2508">
   <si>
     <t>code</t>
   </si>
@@ -7532,6 +7532,12 @@
   </si>
   <si>
     <t>Abdul Latif Jameel Poverty Action Lab at MIT</t>
+  </si>
+  <si>
+    <t>UA-EDR-9795443</t>
+  </si>
+  <si>
+    <t>Centre for Economic Strategy Ukraine</t>
   </si>
 </sst>
 </file>
@@ -7863,7 +7869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1250"/>
+  <dimension ref="A1:G1251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21628,6 +21634,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1251" spans="1:4">
+      <c r="A1251" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3757" uniqueCount="2508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3760" uniqueCount="2510">
   <si>
     <t>code</t>
   </si>
@@ -7310,6 +7310,12 @@
   </si>
   <si>
     <t>Iniciativa Climatica de Mexico</t>
+  </si>
+  <si>
+    <t>XM-DAC-7-PPR-4000002938</t>
+  </si>
+  <si>
+    <t>Global Water Partnership</t>
   </si>
   <si>
     <t>JO-CCD-200006694</t>
@@ -7869,7 +7875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1251"/>
+  <dimension ref="A1:G1252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21645,6 +21651,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1252" spans="1:4">
+      <c r="A1252" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3760" uniqueCount="2510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3763" uniqueCount="2512">
   <si>
     <t>code</t>
   </si>
@@ -7292,6 +7292,12 @@
   </si>
   <si>
     <t>CANADEM</t>
+  </si>
+  <si>
+    <t>ET-CSA-1351</t>
+  </si>
+  <si>
+    <t>Ethiopian Public Health Association</t>
   </si>
   <si>
     <t>NL-KVK-729081140000</t>
@@ -7875,7 +7881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1252"/>
+  <dimension ref="A1:G1253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21662,6 +21668,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1253" spans="1:4">
+      <c r="A1253" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3763" uniqueCount="2512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3769" uniqueCount="2516">
   <si>
     <t>code</t>
   </si>
@@ -883,7 +883,7 @@
     <t>IE-CHY-6410</t>
   </si>
   <si>
-    <t>DÃ³chas - Irish Association of Non Governmental Development Organisations</t>
+    <t>Dóchas - Irish Association of Non Governmental Development Organisations</t>
   </si>
   <si>
     <t>GB-COH-01926828</t>
@@ -1267,7 +1267,7 @@
     <t>FR-3</t>
   </si>
   <si>
-    <t>Agence FranÃ§aise de DÃ©veloppement</t>
+    <t>Agence Française de Développement</t>
   </si>
   <si>
     <t>GB-CHC-209131</t>
@@ -1291,7 +1291,7 @@
     <t>GB-COH-03580586-GEC</t>
   </si>
   <si>
-    <t>Girlsâ Education Challenge â Fund Manager PwC</t>
+    <t>Girls’ Education Challenge – Fund Manager PwC</t>
   </si>
   <si>
     <t>GB-COH-07669775</t>
@@ -1441,7 +1441,7 @@
     <t>CA-4</t>
   </si>
   <si>
-    <t>Canada Department of Finance / MinistÃ¨re des Finances Canada</t>
+    <t>Canada Department of Finance / Ministère des Finances Canada</t>
   </si>
   <si>
     <t>GB-CHC-1105489</t>
@@ -1567,7 +1567,7 @@
     <t>BE-BCE_KBO-0447404580</t>
   </si>
   <si>
-    <t>Avocats Sans FrontiÃ¨res</t>
+    <t>Avocats Sans Frontières</t>
   </si>
   <si>
     <t>US-501c3-522318905</t>
@@ -1789,7 +1789,7 @@
     <t>XM-DAC-301-2</t>
   </si>
   <si>
-    <t>Canada - International Development Research Centre/Centre de recherches pour le dÃ©veloppement international</t>
+    <t>Canada - International Development Research Centre/Centre de recherches pour le développement international</t>
   </si>
   <si>
     <t>GB-CHC-1000717</t>
@@ -2905,7 +2905,7 @@
     <t>NL-KVK-41180885</t>
   </si>
   <si>
-    <t>IUCN Nederlands ComitÃ©</t>
+    <t>IUCN Nederlands Comité</t>
   </si>
   <si>
     <t>NL-KVK-41155305</t>
@@ -3454,6 +3454,12 @@
     <t>UN Pooled Funds</t>
   </si>
   <si>
+    <t>CH-FDJP-66006990023</t>
+  </si>
+  <si>
+    <t>ACT Alliance</t>
+  </si>
+  <si>
     <t>XM-DAC-47064</t>
   </si>
   <si>
@@ -3469,7 +3475,7 @@
     <t>XM-DAC-236</t>
   </si>
   <si>
-    <t>MinistÃ¨re de l'Economie et des Finances du BÃ©nin</t>
+    <t>Ministère de l'Economie et des Finances du Bénin</t>
   </si>
   <si>
     <t>DK-CVR-44623528</t>
@@ -3493,7 +3499,7 @@
     <t>BJ-IFU-3200700033415</t>
   </si>
   <si>
-    <t>SociÃ©tÃ© Nationale des eaux du BÃ©nin (SONEB)</t>
+    <t>Société Nationale des eaux du Bénin (SONEB)</t>
   </si>
   <si>
     <t>LB-MOI-18291</t>
@@ -3667,7 +3673,7 @@
     <t>ML-NIF-400100027H</t>
   </si>
   <si>
-    <t>DNH Mali (Direction Nationale de lâHydraulique du Mali)</t>
+    <t>DNH Mali (Direction Nationale de l’Hydraulique du Mali)</t>
   </si>
   <si>
     <t>US-EIN-13-1624114</t>
@@ -3769,7 +3775,7 @@
     <t>AR-CENOC-16969-A</t>
   </si>
   <si>
-    <t>FundaciÃ³n Fondo Mujeres del Sur</t>
+    <t>Fundación Fondo Mujeres del Sur</t>
   </si>
   <si>
     <t>US-EIN-58-2368165</t>
@@ -3799,7 +3805,7 @@
     <t>MZ-NUIT-700098168</t>
   </si>
   <si>
-    <t>AdministraÃ§Ã£o de Infra-Estruturas de Ãguas e Saneamento</t>
+    <t>Administração de Infra-Estruturas de Águas e Saneamento</t>
   </si>
   <si>
     <t>XM-DAC-46009</t>
@@ -3817,7 +3823,7 @@
     <t>MZ-NUIT-50039061</t>
   </si>
   <si>
-    <t>AgÃªncia de Desenvolvimento do Vale do Zambeze</t>
+    <t>Agência de Desenvolvimento do Vale do Zambeze</t>
   </si>
   <si>
     <t>US-EIN-56-2460366</t>
@@ -3871,7 +3877,7 @@
     <t>BE-BCE_KBO-0408643875</t>
   </si>
   <si>
-    <t>Oxfam SolidaritÃ©-Solidariteit</t>
+    <t>Oxfam Solidarité-Solidariteit</t>
   </si>
   <si>
     <t>US-EIN-33-1112770</t>
@@ -4039,7 +4045,7 @@
     <t>MZ-NUIT-600000381</t>
   </si>
   <si>
-    <t>Fundo de Investimento e Patrimonio do Abastecimento de Ãgua (FIPAG)</t>
+    <t>Fundo de Investimento e Patrimonio do Abastecimento de Água (FIPAG)</t>
   </si>
   <si>
     <t>ZW-PVO-15/2003</t>
@@ -4093,7 +4099,7 @@
     <t>BE-BCE_KBO-0448755949</t>
   </si>
   <si>
-    <t>Collectif StratÃ©gies Alimentaires</t>
+    <t>Collectif Stratégies Alimentaires</t>
   </si>
   <si>
     <t>NL-KVK-34370207</t>
@@ -4177,7 +4183,7 @@
     <t>BE-BCE_KBO-0418015461</t>
   </si>
   <si>
-    <t>Entraide et FraternitÃ©</t>
+    <t>Entraide et Fraternité</t>
   </si>
   <si>
     <t>GB-CHC-1076822</t>
@@ -4189,7 +4195,7 @@
     <t>BE-BCE_KBO-0422717486</t>
   </si>
   <si>
-    <t>Louvain CoopÃ©ration</t>
+    <t>Louvain Coopération</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0451516390</t>
@@ -4201,7 +4207,7 @@
     <t>BE-BCE_KBO-0421207751</t>
   </si>
   <si>
-    <t>Centre National de CoopÃ©ration au DÃ©veloppement (CNCD-11.11.11)</t>
+    <t>Centre National de Coopération au Développement (CNCD-11.11.11)</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0418282311</t>
@@ -4267,7 +4273,7 @@
     <t>BE-BCE_KBO-0413986102</t>
   </si>
   <si>
-    <t>Wereldsolidariteit-SolidaritÃ© Mondiale (WSM)</t>
+    <t>Wereldsolidariteit-Solidarité Mondiale (WSM)</t>
   </si>
   <si>
     <t>NG-CAC-692943</t>
@@ -4309,7 +4315,7 @@
     <t>BE-BCE_KBO-0415627875</t>
   </si>
   <si>
-    <t>ULB-CoopÃ©ration</t>
+    <t>ULB-Coopération</t>
   </si>
   <si>
     <t>DK-CVR-37295728</t>
@@ -4345,7 +4351,7 @@
     <t>BE-BCE_KBO-0408628435</t>
   </si>
   <si>
-    <t>SOS Kinderdorpen BelgiÃ« / SOS Villages d'Enfants Belgique</t>
+    <t>SOS Kinderdorpen België / SOS Villages d'Enfants Belgique</t>
   </si>
   <si>
     <t>ET-CSA-1233</t>
@@ -4375,7 +4381,7 @@
     <t>BE-BCE_KBO-0462132150</t>
   </si>
   <si>
-    <t>Croix-Rouge de Belgique CommunautÃ© francophone - ActivitÃ©s internationales ASBL</t>
+    <t>Croix-Rouge de Belgique Communauté francophone - Activités internationales ASBL</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0431955945</t>
@@ -4387,19 +4393,19 @@
     <t>BE-BCE_KBO-0415880570</t>
   </si>
   <si>
-    <t>Association pour la Promotion de l'Education et de la Formation Ã  l'Etranger</t>
+    <t>Association pour la Promotion de l'Education et de la Formation à l'Etranger</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0433439550</t>
   </si>
   <si>
-    <t>DÃ©fi Belgique Afrique</t>
+    <t>Défi Belgique Afrique</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0463455904</t>
   </si>
   <si>
-    <t>ChaÃ®ne de l'Espoir Belgique / Keten van Hoop BelgiÃ« / Chain of Hope Belgium</t>
+    <t>Chaîne de l'Espoir Belgique / Keten van Hoop België / Chain of Hope Belgium</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0432235661</t>
@@ -4435,13 +4441,13 @@
     <t>BE-BCE_KBO-0454555163</t>
   </si>
   <si>
-    <t>RCN Justice &amp; DÃ©mocratie</t>
+    <t>RCN Justice &amp; Démocratie</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0460162753</t>
   </si>
   <si>
-    <t>Medecins du Monde Belgique - Dokters van de Wereld BelgÃ¯e</t>
+    <t>Medecins du Monde Belgique - Dokters van de Wereld Belgïe</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0413119733</t>
@@ -4495,7 +4501,7 @@
     <t>BE-BCE_KBO-0478060441</t>
   </si>
   <si>
-    <t>Beweging voor Internationale Solidariteit - Mouvement pour la SolidaritÃ© Internationale</t>
+    <t>Beweging voor Internationale Solidariteit - Mouvement pour la Solidarité Internationale</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0479222461</t>
@@ -4525,13 +4531,13 @@
     <t>BE-BCE_KBO-0408095925</t>
   </si>
   <si>
-    <t>Auto-DÃ©veloppement Afrique (ADA)</t>
+    <t>Auto-Développement Afrique (ADA)</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0416934803</t>
   </si>
   <si>
-    <t>Forum Universitaire pour la CoopÃ©ration Internationale au DÃ©veloppement -FUCID ASBL</t>
+    <t>Forum Universitaire pour la Coopération Internationale au Développement -FUCID ASBL</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0418399305</t>
@@ -4639,7 +4645,7 @@
     <t>BE-BCE_KBO-0546740696</t>
   </si>
   <si>
-    <t>AcadÃ©mie de recherche et d'enseignement supÃ©rieur</t>
+    <t>Académie de recherche et d'enseignement supérieur</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0474912493</t>
@@ -4663,19 +4669,19 @@
     <t>BE-BCE_KBO-0448723978</t>
   </si>
   <si>
-    <t>MÃ©decins Sans Vacances</t>
+    <t>Médecins Sans Vacances</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0446340550</t>
   </si>
   <si>
-    <t>ComitÃ© pour l'abolition des dettes illÃ©gitimes</t>
+    <t>Comité pour l'abolition des dettes illégitimes</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0415499795</t>
   </si>
   <si>
-    <t>ITECO - Centre de formation pour le dÃ©veloppement</t>
+    <t>ITECO - Centre de formation pour le développement</t>
   </si>
   <si>
     <t>NL-KVK-40478591</t>
@@ -4735,7 +4741,7 @@
     <t>BE-BCE_KBO-0417549465</t>
   </si>
   <si>
-    <t>CoopÃ©ration par l'Education et la Culture</t>
+    <t>Coopération par l'Education et la Culture</t>
   </si>
   <si>
     <t>DK-CVR-25191501</t>
@@ -4753,7 +4759,7 @@
     <t>CO-RUE-860049972</t>
   </si>
   <si>
-    <t>FundaciÃ³n OriÃ©ntame</t>
+    <t>Fundación Oriéntame</t>
   </si>
   <si>
     <t>CH-FDJP-CHE102197003</t>
@@ -4927,7 +4933,7 @@
     <t>ES-CIF-G-8236803</t>
   </si>
   <si>
-    <t>Oxfam IntermÃ³n</t>
+    <t>Oxfam Intermón</t>
   </si>
   <si>
     <t>XM-DAC-41123</t>
@@ -5119,7 +5125,7 @@
     <t>GB-GOV-14</t>
   </si>
   <si>
-    <t>UK â Department for Education</t>
+    <t>UK – Department for Education</t>
   </si>
   <si>
     <t>US-EIN-27-1661997</t>
@@ -5419,109 +5425,109 @@
     <t>BJ-IFU-6201810251129</t>
   </si>
   <si>
-    <t>Commune de Adjarra - BÃ©nin</t>
+    <t>Commune de Adjarra - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201000068802</t>
   </si>
   <si>
-    <t>Commune de Parakou - BÃ©nin</t>
+    <t>Commune de Parakou - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-5200081145006</t>
   </si>
   <si>
-    <t>Commune de Toffo - BÃ©nin</t>
+    <t>Commune de Toffo - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6200901945503</t>
   </si>
   <si>
-    <t>Commune de Toviklin - BÃ©nin</t>
+    <t>Commune de Toviklin - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201101182902</t>
   </si>
   <si>
-    <t>Commune de KpomassÃ¨ - BÃ©nin</t>
+    <t>Commune de Kpomassè - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6200801257400</t>
   </si>
   <si>
-    <t>Commune de ZÃ¨ - BÃ©nin</t>
+    <t>Commune de Zè - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201501755307</t>
   </si>
   <si>
-    <t>Commune de Allada - BÃ©nin</t>
+    <t>Commune de Allada - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201001076902</t>
   </si>
   <si>
-    <t>Commune de AplahouÃ© - BÃ©nin</t>
+    <t>Commune de Aplahoué - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6200901944805</t>
   </si>
   <si>
-    <t>Commune de Lalo - BÃ©nin</t>
+    <t>Commune de Lalo - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6200901851300</t>
   </si>
   <si>
-    <t>Commune de KÃ©tou - BÃ©nin</t>
+    <t>Commune de Kétou - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-5200801335602</t>
   </si>
   <si>
-    <t>Commune de Adjohoun - BÃ©nin</t>
+    <t>Commune de Adjohoun - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6200901944008</t>
   </si>
   <si>
-    <t>Commune de Adja-Ouere - BÃ©nin</t>
+    <t>Commune de Adja-Ouere - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201200579608</t>
   </si>
   <si>
-    <t>Commune de PobÃ¨ - BÃ©nin</t>
+    <t>Commune de Pobè - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6200901944209</t>
   </si>
   <si>
-    <t>Commune de Bopa - BÃ©nin</t>
+    <t>Commune de Bopa - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201001843703</t>
   </si>
   <si>
-    <t>Commune de Akpro-MissÃ©rÃ©tÃ© - BÃ©nin</t>
+    <t>Commune de Akpro-Missérété - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201000370801</t>
   </si>
   <si>
-    <t>Commune de ComÃ¨ - BÃ©nin</t>
+    <t>Commune de Comè - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201300688700</t>
   </si>
   <si>
-    <t>Commune de Avrankou - BÃ©nin</t>
+    <t>Commune de Avrankou - Bénin</t>
   </si>
   <si>
     <t>BJ-IFU-6201100143407</t>
   </si>
   <si>
-    <t>Commune de Ifangni - BÃ©nin</t>
+    <t>Commune de Ifangni - Bénin</t>
   </si>
   <si>
     <t>SE-ON-802004-1524</t>
@@ -5533,7 +5539,7 @@
     <t>BJ-IFU-6201100034408</t>
   </si>
   <si>
-    <t>Commune de KlouÃ©kanmÃ¨ - BÃ©nin</t>
+    <t>Commune de Klouékanmè - Bénin</t>
   </si>
   <si>
     <t>KE-KRA-P051502549C</t>
@@ -5725,7 +5731,7 @@
     <t>MZ-NUIT-500004037</t>
   </si>
   <si>
-    <t>DirecÃ§Ã£o Provincial de SaÃºde de Nampula</t>
+    <t>Direcção Provincial de Saúde de Nampula</t>
   </si>
   <si>
     <t>KE-KRA-P051097200R</t>
@@ -5791,7 +5797,7 @@
     <t>DK-CVR-14723692</t>
   </si>
   <si>
-    <t>Mission Ãst</t>
+    <t>Mission Øst</t>
   </si>
   <si>
     <t>GB-COH-RC000297</t>
@@ -5800,6 +5806,12 @@
     <t>King's College London</t>
   </si>
   <si>
+    <t>DK-CVR-16077593</t>
+  </si>
+  <si>
+    <t>Confederation of Danish Industry</t>
+  </si>
+  <si>
     <t>NL-KVK-50130536</t>
   </si>
   <si>
@@ -5977,13 +5989,13 @@
     <t>ML-NIF-082208943A</t>
   </si>
   <si>
-    <t>Groupe Pivot SantÃ© Population</t>
+    <t>Groupe Pivot Santé Population</t>
   </si>
   <si>
     <t>MZ-NUIT-700179850</t>
   </si>
   <si>
-    <t>Plataforma MoÃ§ambicana da Ãgua (PLAMA)</t>
+    <t>Plataforma Moçambicana da Água (PLAMA)</t>
   </si>
   <si>
     <t>UG-RSB-80010003259159/105066</t>
@@ -6049,7 +6061,7 @@
     <t>DK-CVR-20356731</t>
   </si>
   <si>
-    <t>PlanBÃ¸rnefonden</t>
+    <t>PlanBørnefonden</t>
   </si>
   <si>
     <t>NL-KVK-32092131</t>
@@ -6313,7 +6325,7 @@
     <t>FR-RCS-78049888700022</t>
   </si>
   <si>
-    <t>Centre International de DÃ©veloppement et de Recherche</t>
+    <t>Centre International de Développement et de Recherche</t>
   </si>
   <si>
     <t>GB-COH-RC000749</t>
@@ -6379,7 +6391,7 @@
     <t>MZ-MOJ-100717344</t>
   </si>
   <si>
-    <t>IMD MoÃ§ambique</t>
+    <t>IMD Moçambique</t>
   </si>
   <si>
     <t>GB-CHC-1081769</t>
@@ -6649,7 +6661,7 @@
     <t>FR-RCS-40885667200030</t>
   </si>
   <si>
-    <t>Triangle GÃ©nÃ©ration Humanitaire</t>
+    <t>Triangle Génération Humanitaire</t>
   </si>
   <si>
     <t>US-EIN-20-8530747</t>
@@ -6703,7 +6715,7 @@
     <t>CH-FDJP-CHE106823242</t>
   </si>
   <si>
-    <t>Terre des hommes- Aide Ã  l'enfance dans le monde- Fondation</t>
+    <t>Terre des hommes- Aide à l'enfance dans le monde- Fondation</t>
   </si>
   <si>
     <t>GB-SC-015096</t>
@@ -6919,7 +6931,7 @@
     <t>FR-RCS-49962201700014</t>
   </si>
   <si>
-    <t>BibliothÃ¨ques Sans FrontiÃ¨res</t>
+    <t>Bibliothèques Sans Frontières</t>
   </si>
   <si>
     <t>SE-ON-802425-8702</t>
@@ -7195,7 +7207,7 @@
     <t>NL-KVK-64460789</t>
   </si>
   <si>
-    <t>CoÃ¶peratief Climate Fund Managers U.A.</t>
+    <t>Coöperatief Climate Fund Managers U.A.</t>
   </si>
   <si>
     <t>CH-FDJP-CHE251665168</t>
@@ -7231,7 +7243,7 @@
     <t>GB-CHC-1187935</t>
   </si>
   <si>
-    <t>International Campaign WomenÂ´s Right to Safe Abortion</t>
+    <t>International Campaign Women´s Right to Safe Abortion</t>
   </si>
   <si>
     <t>GB-CHC-208223</t>
@@ -7279,7 +7291,7 @@
     <t>ML-NIF-084106436R</t>
   </si>
   <si>
-    <t>Conseil et Appui pour l'Education Ã  la Base Mali</t>
+    <t>Conseil et Appui pour l'Education à la Base Mali</t>
   </si>
   <si>
     <t>GB-COH-07840888</t>
@@ -7387,7 +7399,7 @@
     <t>US-EIN-82-0644678</t>
   </si>
   <si>
-    <t>SynergÃ­a - Initiatives for Human Rights</t>
+    <t>Synergía - Initiatives for Human Rights</t>
   </si>
   <si>
     <t>GB-COH-11594545</t>
@@ -7441,7 +7453,7 @@
     <t>MX-RFC-SLP1412039F3</t>
   </si>
   <si>
-    <t>Soluciones en LegislaciÃ³n y PolÃ­tica Ambiental AC</t>
+    <t>Soluciones en Legislación y Política Ambiental AC</t>
   </si>
   <si>
     <t>GB-CHC-1166956</t>
@@ -7881,7 +7893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1253"/>
+  <dimension ref="A1:G1255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21679,6 +21691,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1254" spans="1:4">
+      <c r="A1254" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>2513</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4">
+      <c r="A1255" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>2515</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="2517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3778" uniqueCount="2520">
   <si>
     <t>code</t>
   </si>
@@ -7315,12 +7315,15 @@
     <t>Ethiopian Public Health Association</t>
   </si>
   <si>
+    <t>NL-KVK-72908114</t>
+  </si>
+  <si>
+    <t>The AGRI3 Fund</t>
+  </si>
+  <si>
     <t>NL-KVK-729081140000</t>
   </si>
   <si>
-    <t>The AGRI3 Fund</t>
-  </si>
-  <si>
     <t>YE-MSAL-49-M-2019</t>
   </si>
   <si>
@@ -7559,6 +7562,12 @@
   </si>
   <si>
     <t>Abdul Latif Jameel Poverty Action Lab at MIT</t>
+  </si>
+  <si>
+    <t>BI-NIF-4000742330</t>
+  </si>
+  <si>
+    <t>AUXFIN Burundi</t>
   </si>
   <si>
     <t>UA-EDR-9795443</t>
@@ -7896,7 +7905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1256"/>
+  <dimension ref="A1:G1258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21281,7 +21290,7 @@
         <v>2435</v>
       </c>
       <c r="B1216" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="D1216" t="s">
         <v>9</v>
@@ -21289,10 +21298,10 @@
     </row>
     <row r="1217" spans="1:4">
       <c r="A1217" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B1217" t="s">
         <v>2437</v>
-      </c>
-      <c r="B1217" t="s">
-        <v>2438</v>
       </c>
       <c r="D1217" t="s">
         <v>9</v>
@@ -21300,10 +21309,10 @@
     </row>
     <row r="1218" spans="1:4">
       <c r="A1218" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B1218" t="s">
         <v>2439</v>
-      </c>
-      <c r="B1218" t="s">
-        <v>2440</v>
       </c>
       <c r="D1218" t="s">
         <v>9</v>
@@ -21311,10 +21320,10 @@
     </row>
     <row r="1219" spans="1:4">
       <c r="A1219" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B1219" t="s">
         <v>2441</v>
-      </c>
-      <c r="B1219" t="s">
-        <v>2442</v>
       </c>
       <c r="D1219" t="s">
         <v>9</v>
@@ -21322,10 +21331,10 @@
     </row>
     <row r="1220" spans="1:4">
       <c r="A1220" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B1220" t="s">
         <v>2443</v>
-      </c>
-      <c r="B1220" t="s">
-        <v>2444</v>
       </c>
       <c r="D1220" t="s">
         <v>9</v>
@@ -21333,10 +21342,10 @@
     </row>
     <row r="1221" spans="1:4">
       <c r="A1221" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B1221" t="s">
         <v>2445</v>
-      </c>
-      <c r="B1221" t="s">
-        <v>2446</v>
       </c>
       <c r="D1221" t="s">
         <v>9</v>
@@ -21344,10 +21353,10 @@
     </row>
     <row r="1222" spans="1:4">
       <c r="A1222" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B1222" t="s">
         <v>2447</v>
-      </c>
-      <c r="B1222" t="s">
-        <v>2448</v>
       </c>
       <c r="D1222" t="s">
         <v>9</v>
@@ -21355,10 +21364,10 @@
     </row>
     <row r="1223" spans="1:4">
       <c r="A1223" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B1223" t="s">
         <v>2449</v>
-      </c>
-      <c r="B1223" t="s">
-        <v>2450</v>
       </c>
       <c r="D1223" t="s">
         <v>9</v>
@@ -21366,10 +21375,10 @@
     </row>
     <row r="1224" spans="1:4">
       <c r="A1224" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B1224" t="s">
         <v>2451</v>
-      </c>
-      <c r="B1224" t="s">
-        <v>2452</v>
       </c>
       <c r="D1224" t="s">
         <v>9</v>
@@ -21377,10 +21386,10 @@
     </row>
     <row r="1225" spans="1:4">
       <c r="A1225" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B1225" t="s">
         <v>2453</v>
-      </c>
-      <c r="B1225" t="s">
-        <v>2454</v>
       </c>
       <c r="D1225" t="s">
         <v>9</v>
@@ -21388,10 +21397,10 @@
     </row>
     <row r="1226" spans="1:4">
       <c r="A1226" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B1226" t="s">
         <v>2455</v>
-      </c>
-      <c r="B1226" t="s">
-        <v>2456</v>
       </c>
       <c r="D1226" t="s">
         <v>9</v>
@@ -21399,10 +21408,10 @@
     </row>
     <row r="1227" spans="1:4">
       <c r="A1227" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B1227" t="s">
         <v>2457</v>
-      </c>
-      <c r="B1227" t="s">
-        <v>2458</v>
       </c>
       <c r="D1227" t="s">
         <v>9</v>
@@ -21410,10 +21419,10 @@
     </row>
     <row r="1228" spans="1:4">
       <c r="A1228" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B1228" t="s">
         <v>2459</v>
-      </c>
-      <c r="B1228" t="s">
-        <v>2460</v>
       </c>
       <c r="D1228" t="s">
         <v>9</v>
@@ -21421,10 +21430,10 @@
     </row>
     <row r="1229" spans="1:4">
       <c r="A1229" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B1229" t="s">
         <v>2461</v>
-      </c>
-      <c r="B1229" t="s">
-        <v>2462</v>
       </c>
       <c r="D1229" t="s">
         <v>9</v>
@@ -21432,10 +21441,10 @@
     </row>
     <row r="1230" spans="1:4">
       <c r="A1230" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B1230" t="s">
         <v>2463</v>
-      </c>
-      <c r="B1230" t="s">
-        <v>2464</v>
       </c>
       <c r="D1230" t="s">
         <v>9</v>
@@ -21443,10 +21452,10 @@
     </row>
     <row r="1231" spans="1:4">
       <c r="A1231" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B1231" t="s">
         <v>2465</v>
-      </c>
-      <c r="B1231" t="s">
-        <v>2466</v>
       </c>
       <c r="D1231" t="s">
         <v>9</v>
@@ -21454,10 +21463,10 @@
     </row>
     <row r="1232" spans="1:4">
       <c r="A1232" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B1232" t="s">
         <v>2467</v>
-      </c>
-      <c r="B1232" t="s">
-        <v>2468</v>
       </c>
       <c r="D1232" t="s">
         <v>9</v>
@@ -21465,10 +21474,10 @@
     </row>
     <row r="1233" spans="1:4">
       <c r="A1233" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B1233" t="s">
         <v>2469</v>
-      </c>
-      <c r="B1233" t="s">
-        <v>2470</v>
       </c>
       <c r="D1233" t="s">
         <v>9</v>
@@ -21476,10 +21485,10 @@
     </row>
     <row r="1234" spans="1:4">
       <c r="A1234" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B1234" t="s">
         <v>2471</v>
-      </c>
-      <c r="B1234" t="s">
-        <v>2472</v>
       </c>
       <c r="D1234" t="s">
         <v>9</v>
@@ -21487,10 +21496,10 @@
     </row>
     <row r="1235" spans="1:4">
       <c r="A1235" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B1235" t="s">
         <v>2473</v>
-      </c>
-      <c r="B1235" t="s">
-        <v>2474</v>
       </c>
       <c r="D1235" t="s">
         <v>9</v>
@@ -21498,10 +21507,10 @@
     </row>
     <row r="1236" spans="1:4">
       <c r="A1236" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B1236" t="s">
         <v>2475</v>
-      </c>
-      <c r="B1236" t="s">
-        <v>2476</v>
       </c>
       <c r="D1236" t="s">
         <v>9</v>
@@ -21509,10 +21518,10 @@
     </row>
     <row r="1237" spans="1:4">
       <c r="A1237" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B1237" t="s">
         <v>2477</v>
-      </c>
-      <c r="B1237" t="s">
-        <v>2478</v>
       </c>
       <c r="D1237" t="s">
         <v>9</v>
@@ -21520,10 +21529,10 @@
     </row>
     <row r="1238" spans="1:4">
       <c r="A1238" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B1238" t="s">
         <v>2479</v>
-      </c>
-      <c r="B1238" t="s">
-        <v>2480</v>
       </c>
       <c r="D1238" t="s">
         <v>9</v>
@@ -21531,10 +21540,10 @@
     </row>
     <row r="1239" spans="1:4">
       <c r="A1239" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B1239" t="s">
         <v>2481</v>
-      </c>
-      <c r="B1239" t="s">
-        <v>2482</v>
       </c>
       <c r="D1239" t="s">
         <v>9</v>
@@ -21542,10 +21551,10 @@
     </row>
     <row r="1240" spans="1:4">
       <c r="A1240" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B1240" t="s">
         <v>2483</v>
-      </c>
-      <c r="B1240" t="s">
-        <v>2484</v>
       </c>
       <c r="D1240" t="s">
         <v>9</v>
@@ -21553,10 +21562,10 @@
     </row>
     <row r="1241" spans="1:4">
       <c r="A1241" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B1241" t="s">
         <v>2485</v>
-      </c>
-      <c r="B1241" t="s">
-        <v>2486</v>
       </c>
       <c r="D1241" t="s">
         <v>9</v>
@@ -21564,10 +21573,10 @@
     </row>
     <row r="1242" spans="1:4">
       <c r="A1242" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B1242" t="s">
         <v>2487</v>
-      </c>
-      <c r="B1242" t="s">
-        <v>2488</v>
       </c>
       <c r="D1242" t="s">
         <v>9</v>
@@ -21575,10 +21584,10 @@
     </row>
     <row r="1243" spans="1:4">
       <c r="A1243" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B1243" t="s">
         <v>2489</v>
-      </c>
-      <c r="B1243" t="s">
-        <v>2490</v>
       </c>
       <c r="D1243" t="s">
         <v>9</v>
@@ -21586,10 +21595,10 @@
     </row>
     <row r="1244" spans="1:4">
       <c r="A1244" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B1244" t="s">
         <v>2491</v>
-      </c>
-      <c r="B1244" t="s">
-        <v>2492</v>
       </c>
       <c r="D1244" t="s">
         <v>9</v>
@@ -21597,10 +21606,10 @@
     </row>
     <row r="1245" spans="1:4">
       <c r="A1245" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B1245" t="s">
         <v>2493</v>
-      </c>
-      <c r="B1245" t="s">
-        <v>2494</v>
       </c>
       <c r="D1245" t="s">
         <v>9</v>
@@ -21608,10 +21617,10 @@
     </row>
     <row r="1246" spans="1:4">
       <c r="A1246" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B1246" t="s">
         <v>2495</v>
-      </c>
-      <c r="B1246" t="s">
-        <v>2496</v>
       </c>
       <c r="D1246" t="s">
         <v>9</v>
@@ -21619,10 +21628,10 @@
     </row>
     <row r="1247" spans="1:4">
       <c r="A1247" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B1247" t="s">
         <v>2497</v>
-      </c>
-      <c r="B1247" t="s">
-        <v>2498</v>
       </c>
       <c r="D1247" t="s">
         <v>9</v>
@@ -21630,10 +21639,10 @@
     </row>
     <row r="1248" spans="1:4">
       <c r="A1248" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B1248" t="s">
         <v>2499</v>
-      </c>
-      <c r="B1248" t="s">
-        <v>2500</v>
       </c>
       <c r="D1248" t="s">
         <v>9</v>
@@ -21641,10 +21650,10 @@
     </row>
     <row r="1249" spans="1:4">
       <c r="A1249" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B1249" t="s">
         <v>2501</v>
-      </c>
-      <c r="B1249" t="s">
-        <v>2502</v>
       </c>
       <c r="D1249" t="s">
         <v>9</v>
@@ -21652,10 +21661,10 @@
     </row>
     <row r="1250" spans="1:4">
       <c r="A1250" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B1250" t="s">
         <v>2503</v>
-      </c>
-      <c r="B1250" t="s">
-        <v>2504</v>
       </c>
       <c r="D1250" t="s">
         <v>9</v>
@@ -21663,10 +21672,10 @@
     </row>
     <row r="1251" spans="1:4">
       <c r="A1251" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B1251" t="s">
         <v>2505</v>
-      </c>
-      <c r="B1251" t="s">
-        <v>2506</v>
       </c>
       <c r="D1251" t="s">
         <v>9</v>
@@ -21674,10 +21683,10 @@
     </row>
     <row r="1252" spans="1:4">
       <c r="A1252" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B1252" t="s">
         <v>2507</v>
-      </c>
-      <c r="B1252" t="s">
-        <v>2508</v>
       </c>
       <c r="D1252" t="s">
         <v>9</v>
@@ -21685,10 +21694,10 @@
     </row>
     <row r="1253" spans="1:4">
       <c r="A1253" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B1253" t="s">
         <v>2509</v>
-      </c>
-      <c r="B1253" t="s">
-        <v>2510</v>
       </c>
       <c r="D1253" t="s">
         <v>9</v>
@@ -21696,10 +21705,10 @@
     </row>
     <row r="1254" spans="1:4">
       <c r="A1254" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B1254" t="s">
         <v>2511</v>
-      </c>
-      <c r="B1254" t="s">
-        <v>2512</v>
       </c>
       <c r="D1254" t="s">
         <v>9</v>
@@ -21707,10 +21716,10 @@
     </row>
     <row r="1255" spans="1:4">
       <c r="A1255" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B1255" t="s">
         <v>2513</v>
-      </c>
-      <c r="B1255" t="s">
-        <v>2514</v>
       </c>
       <c r="D1255" t="s">
         <v>9</v>
@@ -21718,12 +21727,34 @@
     </row>
     <row r="1256" spans="1:4">
       <c r="A1256" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B1256" t="s">
         <v>2515</v>
       </c>
-      <c r="B1256" t="s">
+      <c r="D1256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4">
+      <c r="A1257" t="s">
         <v>2516</v>
       </c>
-      <c r="D1256" t="s">
+      <c r="B1257" t="s">
+        <v>2517</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4">
+      <c r="A1258" t="s">
+        <v>2518</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>2519</v>
+      </c>
+      <c r="D1258" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3778" uniqueCount="2520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="2524">
   <si>
     <t>code</t>
   </si>
@@ -7570,10 +7570,22 @@
     <t>AUXFIN Burundi</t>
   </si>
   <si>
+    <t>MY-SSM-1172311D</t>
+  </si>
+  <si>
+    <t>Forever Sabah</t>
+  </si>
+  <si>
     <t>UA-EDR-9795443</t>
   </si>
   <si>
     <t>Centre for Economic Strategy Ukraine</t>
+  </si>
+  <si>
+    <t>FR-INSEE-31827645800037</t>
+  </si>
+  <si>
+    <t>Association de solidarité internationale, Agriculteurs français et développement international (Afdi) France</t>
   </si>
 </sst>
 </file>
@@ -7905,7 +7917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1258"/>
+  <dimension ref="A1:G1260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21758,6 +21770,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1259" spans="1:4">
+      <c r="A1259" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>2521</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4">
+      <c r="A1260" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="2524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="2526">
   <si>
     <t>code</t>
   </si>
@@ -7550,6 +7550,12 @@
   </si>
   <si>
     <t>Prospero Limited</t>
+  </si>
+  <si>
+    <t>GB-COH-RC000679</t>
+  </si>
+  <si>
+    <t>University of York</t>
   </si>
   <si>
     <t>XM-DAC-41149</t>
@@ -7917,7 +7923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1260"/>
+  <dimension ref="A1:G1261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21792,6 +21798,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1261" spans="1:4">
+      <c r="A1261" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3787" uniqueCount="2526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="2528">
   <si>
     <t>code</t>
   </si>
@@ -7352,6 +7352,12 @@
   </si>
   <si>
     <t>NLR Indonesia</t>
+  </si>
+  <si>
+    <t>GB-CHC-1076722</t>
+  </si>
+  <si>
+    <t>TRAFFIC International</t>
   </si>
   <si>
     <t>US-EIN-81-2339233</t>
@@ -7923,7 +7929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1261"/>
+  <dimension ref="A1:G1262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21809,6 +21815,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1262" spans="1:4">
+      <c r="A1262" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>2527</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="2528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="2530">
   <si>
     <t>code</t>
   </si>
@@ -7568,6 +7568,12 @@
   </si>
   <si>
     <t>United Nations Development Coordination Office</t>
+  </si>
+  <si>
+    <t>GB-COH-02871809</t>
+  </si>
+  <si>
+    <t>Global Witness</t>
   </si>
   <si>
     <t>US-EIN-042103594</t>
@@ -7929,7 +7935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1262"/>
+  <dimension ref="A1:G1263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21826,6 +21832,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1263" spans="1:4">
+      <c r="A1263" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="2530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3796" uniqueCount="2532">
   <si>
     <t>code</t>
   </si>
@@ -7604,6 +7604,12 @@
   </si>
   <si>
     <t>Association de solidarité internationale, Agriculteurs français et développement international (Afdi) France</t>
+  </si>
+  <si>
+    <t>GB-CHC-1137523</t>
+  </si>
+  <si>
+    <t>The Proforest Initiative UK</t>
   </si>
 </sst>
 </file>
@@ -7935,7 +7941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1263"/>
+  <dimension ref="A1:G1264"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21843,6 +21849,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1264" spans="1:4">
+      <c r="A1264" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>2531</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3796" uniqueCount="2532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3799" uniqueCount="2534">
   <si>
     <t>code</t>
   </si>
@@ -7604,6 +7604,12 @@
   </si>
   <si>
     <t>Association de solidarité internationale, Agriculteurs français et développement international (Afdi) France</t>
+  </si>
+  <si>
+    <t>BR-CNPJ-14.563.354/0001-50</t>
+  </si>
+  <si>
+    <t>Instituto BVRio</t>
   </si>
   <si>
     <t>GB-CHC-1137523</t>
@@ -7941,7 +7947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1264"/>
+  <dimension ref="A1:G1265"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21860,6 +21866,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1265" spans="1:4">
+      <c r="A1265" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3799" uniqueCount="2534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3802" uniqueCount="2536">
   <si>
     <t>code</t>
   </si>
@@ -6665,6 +6665,12 @@
   </si>
   <si>
     <t>Triangle Génération Humanitaire</t>
+  </si>
+  <si>
+    <t>AU-ABN-42097054165</t>
+  </si>
+  <si>
+    <t>Land Equity International</t>
   </si>
   <si>
     <t>US-EIN-20-8530747</t>
@@ -7947,7 +7953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1265"/>
+  <dimension ref="A1:G1266"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21332,7 +21338,7 @@
         <v>2435</v>
       </c>
       <c r="B1216" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="D1216" t="s">
         <v>9</v>
@@ -21340,10 +21346,10 @@
     </row>
     <row r="1217" spans="1:4">
       <c r="A1217" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B1217" t="s">
         <v>2436</v>
-      </c>
-      <c r="B1217" t="s">
-        <v>2437</v>
       </c>
       <c r="D1217" t="s">
         <v>9</v>
@@ -21874,6 +21880,17 @@
         <v>2533</v>
       </c>
       <c r="D1265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4">
+      <c r="A1266" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D1266" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3802" uniqueCount="2536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3808" uniqueCount="2540">
   <si>
     <t>code</t>
   </si>
@@ -7087,6 +7087,12 @@
     <t>African Women's Development and Communication Network</t>
   </si>
   <si>
+    <t>CH-FDJP-CHE296622304</t>
+  </si>
+  <si>
+    <t>The Global Initiative Against Transnational Organized Crime</t>
+  </si>
+  <si>
     <t>LB-MOI-1-100</t>
   </si>
   <si>
@@ -7610,6 +7616,12 @@
   </si>
   <si>
     <t>Association de solidarité internationale, Agriculteurs français et développement international (Afdi) France</t>
+  </si>
+  <si>
+    <t>GB-CHC-1188731</t>
+  </si>
+  <si>
+    <t>Sustainable Hospitality Alliance</t>
   </si>
   <si>
     <t>BR-CNPJ-14.563.354/0001-50</t>
@@ -7953,7 +7965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1266"/>
+  <dimension ref="A1:G1268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21349,7 +21361,7 @@
         <v>2437</v>
       </c>
       <c r="B1217" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="D1217" t="s">
         <v>9</v>
@@ -21357,10 +21369,10 @@
     </row>
     <row r="1218" spans="1:4">
       <c r="A1218" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B1218" t="s">
         <v>2438</v>
-      </c>
-      <c r="B1218" t="s">
-        <v>2439</v>
       </c>
       <c r="D1218" t="s">
         <v>9</v>
@@ -21891,6 +21903,28 @@
         <v>2535</v>
       </c>
       <c r="D1266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4">
+      <c r="A1267" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:4">
+      <c r="A1268" t="s">
+        <v>2538</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>2539</v>
+      </c>
+      <c r="D1268" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3808" uniqueCount="2540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3811" uniqueCount="2542">
   <si>
     <t>code</t>
   </si>
@@ -7628,6 +7628,12 @@
   </si>
   <si>
     <t>Instituto BVRio</t>
+  </si>
+  <si>
+    <t>NL-KVK-861193660</t>
+  </si>
+  <si>
+    <t>OurLoop Stitchting</t>
   </si>
   <si>
     <t>GB-CHC-1137523</t>
@@ -7965,7 +7971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1268"/>
+  <dimension ref="A1:G1269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21928,6 +21934,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1269" spans="1:4">
+      <c r="A1269" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3811" uniqueCount="2542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3817" uniqueCount="2546">
   <si>
     <t>code</t>
   </si>
@@ -6547,6 +6547,12 @@
     <t>Drugs for Neglected Diseases initiative</t>
   </si>
   <si>
+    <t>RW-RRA-103197639</t>
+  </si>
+  <si>
+    <t>Greater Virunga Transboundary Collaboration</t>
+  </si>
+  <si>
     <t>NP-SWC-37725</t>
   </si>
   <si>
@@ -7079,6 +7085,12 @@
   </si>
   <si>
     <t>The United Nations Relief and Works Agency for Palestine Refugees in the Near East (UNRWA)</t>
+  </si>
+  <si>
+    <t>BD-NAB-0918</t>
+  </si>
+  <si>
+    <t>Centre for Policy Dialogue</t>
   </si>
   <si>
     <t>KE-KRA-P000634725S</t>
@@ -7971,7 +7983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1269"/>
+  <dimension ref="A1:G1271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21378,7 +21390,7 @@
         <v>2439</v>
       </c>
       <c r="B1218" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="D1218" t="s">
         <v>9</v>
@@ -21386,10 +21398,10 @@
     </row>
     <row r="1219" spans="1:4">
       <c r="A1219" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="B1219" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D1219" t="s">
         <v>9</v>
@@ -21397,10 +21409,10 @@
     </row>
     <row r="1220" spans="1:4">
       <c r="A1220" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B1220" t="s">
         <v>2442</v>
-      </c>
-      <c r="B1220" t="s">
-        <v>2443</v>
       </c>
       <c r="D1220" t="s">
         <v>9</v>
@@ -21942,6 +21954,28 @@
         <v>2541</v>
       </c>
       <c r="D1269" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:4">
+      <c r="A1270" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:4">
+      <c r="A1271" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>2545</v>
+      </c>
+      <c r="D1271" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3817" uniqueCount="2546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="2548">
   <si>
     <t>code</t>
   </si>
@@ -7556,6 +7556,12 @@
   </si>
   <si>
     <t>JoWomenomics</t>
+  </si>
+  <si>
+    <t>NL-KVK-09108013</t>
+  </si>
+  <si>
+    <t>Advance Consulting</t>
   </si>
   <si>
     <t>XI-GRID-grid.11835.3e</t>
@@ -7983,7 +7989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1271"/>
+  <dimension ref="A1:G1272"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21979,6 +21985,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1272" spans="1:4">
+      <c r="A1272" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>2547</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="2548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3823" uniqueCount="2550">
   <si>
     <t>code</t>
   </si>
@@ -7550,6 +7550,12 @@
   </si>
   <si>
     <t>Northern Ireland Cooperation Overseas Ltd</t>
+  </si>
+  <si>
+    <t>NG-CAC-30547</t>
+  </si>
+  <si>
+    <t>Paradigm Initiative</t>
   </si>
   <si>
     <t>JO-MSD-200159274</t>
@@ -7989,7 +7995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1272"/>
+  <dimension ref="A1:G1273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21996,6 +22002,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1273" spans="1:4">
+      <c r="A1273" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3823" uniqueCount="2550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="2552">
   <si>
     <t>code</t>
   </si>
@@ -7640,6 +7640,12 @@
   </si>
   <si>
     <t>Association de solidarité internationale, Agriculteurs français et développement international (Afdi) France</t>
+  </si>
+  <si>
+    <t>GB-CHC-1017336</t>
+  </si>
+  <si>
+    <t>Elton John AIDS Foundation</t>
   </si>
   <si>
     <t>GB-CHC-1188731</t>
@@ -7995,7 +8001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1273"/>
+  <dimension ref="A1:G1274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22013,6 +22019,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1274" spans="1:4">
+      <c r="A1274" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="2552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3829" uniqueCount="2554">
   <si>
     <t>code</t>
   </si>
@@ -551,6 +551,12 @@
   </si>
   <si>
     <t>Conciliation Resources</t>
+  </si>
+  <si>
+    <t>GB-CHC-1115482</t>
+  </si>
+  <si>
+    <t>BRAC UK</t>
   </si>
   <si>
     <t>ZA-CIPC-2001/005850/08</t>
@@ -8001,7 +8007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1274"/>
+  <dimension ref="A1:G1275"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21430,7 +21436,7 @@
         <v>2443</v>
       </c>
       <c r="B1220" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="D1220" t="s">
         <v>9</v>
@@ -21438,10 +21444,10 @@
     </row>
     <row r="1221" spans="1:4">
       <c r="A1221" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B1221" t="s">
         <v>2444</v>
-      </c>
-      <c r="B1221" t="s">
-        <v>2445</v>
       </c>
       <c r="D1221" t="s">
         <v>9</v>
@@ -22027,6 +22033,17 @@
         <v>2551</v>
       </c>
       <c r="D1274" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:4">
+      <c r="A1275" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>2553</v>
+      </c>
+      <c r="D1275" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3829" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3832" uniqueCount="2556">
   <si>
     <t>code</t>
   </si>
@@ -7676,6 +7676,12 @@
   </si>
   <si>
     <t>The Proforest Initiative UK</t>
+  </si>
+  <si>
+    <t>US-EIN-13-4052259</t>
+  </si>
+  <si>
+    <t>Media Development Investment Fund</t>
   </si>
 </sst>
 </file>
@@ -8007,7 +8013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1275"/>
+  <dimension ref="A1:G1276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22047,6 +22053,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1276" spans="1:4">
+      <c r="A1276" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3832" uniqueCount="2556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3835" uniqueCount="2558">
   <si>
     <t>code</t>
   </si>
@@ -7676,6 +7676,12 @@
   </si>
   <si>
     <t>The Proforest Initiative UK</t>
+  </si>
+  <si>
+    <t>US-EIN-52-2135531</t>
+  </si>
+  <si>
+    <t>Forest Trends Association</t>
   </si>
   <si>
     <t>US-EIN-13-4052259</t>
@@ -8013,7 +8019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1276"/>
+  <dimension ref="A1:G1277"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22064,6 +22070,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1277" spans="1:4">
+      <c r="A1277" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>2557</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3835" uniqueCount="2558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="2560">
   <si>
     <t>code</t>
   </si>
@@ -7682,6 +7682,12 @@
   </si>
   <si>
     <t>Forest Trends Association</t>
+  </si>
+  <si>
+    <t>GB-COH-02515034</t>
+  </si>
+  <si>
+    <t>Timber Trade Federation Ltd.</t>
   </si>
   <si>
     <t>US-EIN-13-4052259</t>
@@ -8019,7 +8025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1277"/>
+  <dimension ref="A1:G1278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22081,6 +22087,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1278" spans="1:4">
+      <c r="A1278" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="2560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="2562">
   <si>
     <t>code</t>
   </si>
@@ -1871,6 +1871,12 @@
   </si>
   <si>
     <t>Abaseen Foundation UK</t>
+  </si>
+  <si>
+    <t>ML-NIF-086108989R</t>
+  </si>
+  <si>
+    <t>Association de Soutien au Développement des Activités de Population</t>
   </si>
   <si>
     <t>GB-CHC-1069182</t>
@@ -8025,7 +8031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1278"/>
+  <dimension ref="A1:G1279"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21465,7 +21471,7 @@
         <v>2445</v>
       </c>
       <c r="B1221" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="D1221" t="s">
         <v>9</v>
@@ -21473,10 +21479,10 @@
     </row>
     <row r="1222" spans="1:4">
       <c r="A1222" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B1222" t="s">
         <v>2446</v>
-      </c>
-      <c r="B1222" t="s">
-        <v>2447</v>
       </c>
       <c r="D1222" t="s">
         <v>9</v>
@@ -22095,6 +22101,17 @@
         <v>2559</v>
       </c>
       <c r="D1278" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:4">
+      <c r="A1279" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D1279" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="2562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="2564">
   <si>
     <t>code</t>
   </si>
@@ -7688,6 +7688,12 @@
   </si>
   <si>
     <t>Forest Trends Association</t>
+  </si>
+  <si>
+    <t>GB-CHC-1074857</t>
+  </si>
+  <si>
+    <t>Church of England - The Archbishops' Council</t>
   </si>
   <si>
     <t>GB-COH-02515034</t>
@@ -8031,7 +8037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1279"/>
+  <dimension ref="A1:G1280"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22115,6 +22121,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1280" spans="1:4">
+      <c r="A1280" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>2563</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -73,7 +73,7 @@
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
-    <t>European Commission - Directorate-General for International Cooperation and Development</t>
+    <t>European Commission - International Partnerships</t>
   </si>
   <si>
     <t>SE-0</t>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="2564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="2566">
   <si>
     <t>code</t>
   </si>
@@ -73,7 +73,7 @@
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
-    <t>European Commission - International Partnerships</t>
+    <t>European Commission - International Cooperation and Development</t>
   </si>
   <si>
     <t>SE-0</t>
@@ -7622,6 +7622,12 @@
   </si>
   <si>
     <t>Global Witness</t>
+  </si>
+  <si>
+    <t>GB-CHC-1175791</t>
+  </si>
+  <si>
+    <t>Global Anaesthesia Development Partnerships</t>
   </si>
   <si>
     <t>US-EIN-042103594</t>
@@ -8037,7 +8043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1280"/>
+  <dimension ref="A1:G1281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22132,6 +22138,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1281" spans="1:4">
+      <c r="A1281" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="2566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3850" uniqueCount="2568">
   <si>
     <t>code</t>
   </si>
@@ -7538,6 +7538,12 @@
   </si>
   <si>
     <t>Asia Justice and Rights</t>
+  </si>
+  <si>
+    <t>GB-UKPRN-10007790</t>
+  </si>
+  <si>
+    <t>University of Edinburgh</t>
   </si>
   <si>
     <t>KE-KRA-P051335339D</t>
@@ -8043,7 +8049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1281"/>
+  <dimension ref="A1:G1282"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22149,6 +22155,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1282" spans="1:4">
+      <c r="A1282" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3850" uniqueCount="2568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="2572">
   <si>
     <t>code</t>
   </si>
@@ -7117,6 +7117,12 @@
     <t>The Global Initiative Against Transnational Organized Crime</t>
   </si>
   <si>
+    <t>BE-BCE_KBO-0434417468</t>
+  </si>
+  <si>
+    <t>CODEART ASBL</t>
+  </si>
+  <si>
     <t>LB-MOI-1-100</t>
   </si>
   <si>
@@ -7694,6 +7700,12 @@
   </si>
   <si>
     <t>The Proforest Initiative UK</t>
+  </si>
+  <si>
+    <t>US-EIN-843236198</t>
+  </si>
+  <si>
+    <t>Corus International</t>
   </si>
   <si>
     <t>US-EIN-52-2135531</t>
@@ -8049,7 +8061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1282"/>
+  <dimension ref="A1:G1284"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21500,7 +21512,7 @@
         <v>2447</v>
       </c>
       <c r="B1222" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="D1222" t="s">
         <v>9</v>
@@ -21508,10 +21520,10 @@
     </row>
     <row r="1223" spans="1:4">
       <c r="A1223" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B1223" t="s">
         <v>2448</v>
-      </c>
-      <c r="B1223" t="s">
-        <v>2449</v>
       </c>
       <c r="D1223" t="s">
         <v>9</v>
@@ -22163,6 +22175,28 @@
         <v>2567</v>
       </c>
       <c r="D1282" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:4">
+      <c r="A1283" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>2569</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:4">
+      <c r="A1284" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D1284" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3859" uniqueCount="2573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="2575">
   <si>
     <t>code</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>Frontline AIDS</t>
+  </si>
+  <si>
+    <t>XI-IATI-EC_INTPA</t>
+  </si>
+  <si>
+    <t>European Commission - International Partnerships</t>
   </si>
   <si>
     <t>XI-IATI-EC_DEVCO</t>
@@ -8064,7 +8070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1285"/>
+  <dimension ref="A1:G1286"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8260,7 +8266,7 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
@@ -8268,10 +8274,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
@@ -9019,7 +9025,7 @@
         <v>175</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
@@ -9027,10 +9033,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
+        <v>177</v>
+      </c>
+      <c r="B87" t="s">
         <v>176</v>
-      </c>
-      <c r="B87" t="s">
-        <v>177</v>
       </c>
       <c r="D87" t="s">
         <v>9</v>
@@ -21537,7 +21543,7 @@
         <v>2450</v>
       </c>
       <c r="B1224" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="D1224" t="s">
         <v>9</v>
@@ -21545,10 +21551,10 @@
     </row>
     <row r="1225" spans="1:4">
       <c r="A1225" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B1225" t="s">
         <v>2451</v>
-      </c>
-      <c r="B1225" t="s">
-        <v>2452</v>
       </c>
       <c r="D1225" t="s">
         <v>9</v>
@@ -22211,6 +22217,17 @@
         <v>2572</v>
       </c>
       <c r="D1285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:4">
+      <c r="A1286" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D1286" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3862" uniqueCount="2575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3865" uniqueCount="2577">
   <si>
     <t>code</t>
   </si>
@@ -7739,6 +7739,12 @@
   </si>
   <si>
     <t>Media Development Investment Fund</t>
+  </si>
+  <si>
+    <t>BE-BCE_KBO-0464147473</t>
+  </si>
+  <si>
+    <t>Laïcité et Humanisme en Afrique Centrale (LHAC)</t>
   </si>
 </sst>
 </file>
@@ -8070,7 +8076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1286"/>
+  <dimension ref="A1:G1287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22231,6 +22237,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1287" spans="1:4">
+      <c r="A1287" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3865" uniqueCount="2577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3868" uniqueCount="2579">
   <si>
     <t>code</t>
   </si>
@@ -7661,6 +7661,12 @@
   </si>
   <si>
     <t>AUXFIN Burundi</t>
+  </si>
+  <si>
+    <t>MZ-MOJ100094525</t>
+  </si>
+  <si>
+    <t>Micaia Foundation</t>
   </si>
   <si>
     <t>MY-SSM-1172311D</t>
@@ -8076,7 +8082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1287"/>
+  <dimension ref="A1:G1288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -22248,6 +22254,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1288" spans="1:4">
+      <c r="A1288" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3868" uniqueCount="2579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3871" uniqueCount="2581">
   <si>
     <t>code</t>
   </si>
@@ -2120,6 +2120,12 @@
   </si>
   <si>
     <t>Norad - Norwegian Agency for Development Cooperation</t>
+  </si>
+  <si>
+    <t>US-EIN-20-3690821</t>
+  </si>
+  <si>
+    <t>Rights and Resources Initaitive</t>
   </si>
   <si>
     <t>XI-IATI-5914-1107</t>
@@ -8082,7 +8088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1288"/>
+  <dimension ref="A1:G1289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -21566,7 +21572,7 @@
         <v>2452</v>
       </c>
       <c r="B1225" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="D1225" t="s">
         <v>9</v>
@@ -21574,10 +21580,10 @@
     </row>
     <row r="1226" spans="1:4">
       <c r="A1226" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B1226" t="s">
         <v>2453</v>
-      </c>
-      <c r="B1226" t="s">
-        <v>2454</v>
       </c>
       <c r="D1226" t="s">
         <v>9</v>
@@ -22262,6 +22268,17 @@
         <v>2578</v>
       </c>
       <c r="D1288" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:4">
+      <c r="A1289" t="s">
+        <v>2579</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>2580</v>
+      </c>
+      <c r="D1289" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5551" uniqueCount="3680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5575" uniqueCount="3696">
   <si>
     <t>code</t>
   </si>
@@ -9682,6 +9682,12 @@
     <t>Tech2Peace</t>
   </si>
   <si>
+    <t>XM-DAC-47062</t>
+  </si>
+  <si>
+    <t>International Institute of Tropical Agriculture (IITA)</t>
+  </si>
+  <si>
     <t>JO-COA-0301-57112</t>
   </si>
   <si>
@@ -10489,6 +10495,12 @@
     <t>Village Infrastructure Angels</t>
   </si>
   <si>
+    <t>GB-COH-05380206</t>
+  </si>
+  <si>
+    <t>Joint Nature Conservation Committee</t>
+  </si>
+  <si>
     <t>GB-COH-02525806</t>
   </si>
   <si>
@@ -10903,6 +10915,12 @@
     <t>Soul City Institute</t>
   </si>
   <si>
+    <t>ZA-CIP-2007-012585-08</t>
+  </si>
+  <si>
+    <t>Reach Digital Health NPC</t>
+  </si>
+  <si>
     <t>US-EIN-53-0196603</t>
   </si>
   <si>
@@ -10975,6 +10993,12 @@
     <t>Design without Borders Africa</t>
   </si>
   <si>
+    <t>XI-DUNS-499432771</t>
+  </si>
+  <si>
+    <t>Navrongo Health Research Centre</t>
+  </si>
+  <si>
     <t>US-SAM-VJ8RGVMEPAT7</t>
   </si>
   <si>
@@ -11023,6 +11047,12 @@
     <t>Tax Justice Network</t>
   </si>
   <si>
+    <t>ZA-CIP-2022-449689-08</t>
+  </si>
+  <si>
+    <t>Energy Council of South Africa</t>
+  </si>
+  <si>
     <t>FR-INSEE-93282389100019</t>
   </si>
   <si>
@@ -11039,6 +11069,24 @@
   </si>
   <si>
     <t>Clim-Eat</t>
+  </si>
+  <si>
+    <t>SL-NRA-1136607-8</t>
+  </si>
+  <si>
+    <t>Institute of Gender and Children's Health Research</t>
+  </si>
+  <si>
+    <t>SL-OARG-2420280</t>
+  </si>
+  <si>
+    <t>Centre of Dialogue on Human Settlement and Poverty Alleviation (CODOHSAPA)</t>
+  </si>
+  <si>
+    <t>GB-COH-08195029</t>
+  </si>
+  <si>
+    <t>Environmental Finance Limited, trading as Finance Earth</t>
   </si>
   <si>
     <t>US-EIN-52-1780162</t>
@@ -11385,7 +11433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1849"/>
+  <dimension ref="A1:G1857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -29225,7 +29273,7 @@
         <v>3224</v>
       </c>
       <c r="B1621" t="s">
-        <v>3217</v>
+        <v>3225</v>
       </c>
       <c r="D1621" t="s">
         <v>9</v>
@@ -29233,10 +29281,10 @@
     </row>
     <row r="1622" spans="1:4">
       <c r="A1622" t="s">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="B1622" t="s">
-        <v>3226</v>
+        <v>3217</v>
       </c>
       <c r="D1622" t="s">
         <v>9</v>
@@ -31722,7 +31770,7 @@
         <v>3677</v>
       </c>
       <c r="B1848" t="s">
-        <v>3266</v>
+        <v>3678</v>
       </c>
       <c r="D1848" t="s">
         <v>9</v>
@@ -31730,12 +31778,100 @@
     </row>
     <row r="1849" spans="1:4">
       <c r="A1849" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
       <c r="B1849" t="s">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="D1849" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:4">
+      <c r="A1850" t="s">
+        <v>3681</v>
+      </c>
+      <c r="B1850" t="s">
+        <v>3682</v>
+      </c>
+      <c r="D1850" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:4">
+      <c r="A1851" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B1851" t="s">
+        <v>3684</v>
+      </c>
+      <c r="D1851" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:4">
+      <c r="A1852" t="s">
+        <v>3685</v>
+      </c>
+      <c r="B1852" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D1852" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:4">
+      <c r="A1853" t="s">
+        <v>3687</v>
+      </c>
+      <c r="B1853" t="s">
+        <v>3688</v>
+      </c>
+      <c r="D1853" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:4">
+      <c r="A1854" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1854" t="s">
+        <v>3690</v>
+      </c>
+      <c r="D1854" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:4">
+      <c r="A1855" t="s">
+        <v>3691</v>
+      </c>
+      <c r="B1855" t="s">
+        <v>3692</v>
+      </c>
+      <c r="D1855" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:4">
+      <c r="A1856" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>3268</v>
+      </c>
+      <c r="D1856" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:4">
+      <c r="A1857" t="s">
+        <v>3694</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>3695</v>
+      </c>
+      <c r="D1857" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5575" uniqueCount="3696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5578" uniqueCount="3698">
   <si>
     <t>code</t>
   </si>
@@ -11033,6 +11033,12 @@
   </si>
   <si>
     <t>American University of Beirut</t>
+  </si>
+  <si>
+    <t>XI-IATI-CLAD</t>
+  </si>
+  <si>
+    <t>Centro Latinoamericano de Administración para el Desarrollo</t>
   </si>
   <si>
     <t>GB-CHC-1180966</t>
@@ -11433,7 +11439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1857"/>
+  <dimension ref="A1:G1858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -31858,7 +31864,7 @@
         <v>3693</v>
       </c>
       <c r="B1856" t="s">
-        <v>3268</v>
+        <v>3694</v>
       </c>
       <c r="D1856" t="s">
         <v>9</v>
@@ -31866,12 +31872,23 @@
     </row>
     <row r="1857" spans="1:4">
       <c r="A1857" t="s">
-        <v>3694</v>
+        <v>3695</v>
       </c>
       <c r="B1857" t="s">
-        <v>3695</v>
+        <v>3268</v>
       </c>
       <c r="D1857" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:4">
+      <c r="A1858" t="s">
+        <v>3696</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>3697</v>
+      </c>
+      <c r="D1858" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5578" uniqueCount="3698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5593" uniqueCount="3708">
   <si>
     <t>code</t>
   </si>
@@ -10459,6 +10459,12 @@
     <t>Southeast Asia Freedom of Expression Network (SAFEnet)</t>
   </si>
   <si>
+    <t>IT-CF-97050280581</t>
+  </si>
+  <si>
+    <t>Comitato Internazionale per lo Sviluppo dei Popoli</t>
+  </si>
+  <si>
     <t>NG-CAC-6896199</t>
   </si>
   <si>
@@ -11099,6 +11105,30 @@
   </si>
   <si>
     <t>Eurasia Foundation</t>
+  </si>
+  <si>
+    <t>US-EIN-35-2725269</t>
+  </si>
+  <si>
+    <t>Science for Africa Foundation</t>
+  </si>
+  <si>
+    <t>UG-NGO-INDP51781129NB</t>
+  </si>
+  <si>
+    <t>RWENZORI ANTI CORRUP0TION COALITION</t>
+  </si>
+  <si>
+    <t>UA-EDR-42661077</t>
+  </si>
+  <si>
+    <t>Consumer society IMTD-INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>GB-COH-00559784</t>
+  </si>
+  <si>
+    <t>The Pirbright Institute</t>
   </si>
   <si>
     <t>ET-ERCA-0056106666</t>
@@ -11439,7 +11469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1858"/>
+  <dimension ref="A1:G1863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -31875,7 +31905,7 @@
         <v>3695</v>
       </c>
       <c r="B1857" t="s">
-        <v>3268</v>
+        <v>3696</v>
       </c>
       <c r="D1857" t="s">
         <v>9</v>
@@ -31883,12 +31913,67 @@
     </row>
     <row r="1858" spans="1:4">
       <c r="A1858" t="s">
-        <v>3696</v>
+        <v>3697</v>
       </c>
       <c r="B1858" t="s">
-        <v>3697</v>
+        <v>3698</v>
       </c>
       <c r="D1858" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:4">
+      <c r="A1859" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>3700</v>
+      </c>
+      <c r="D1859" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:4">
+      <c r="A1860" t="s">
+        <v>3701</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>3702</v>
+      </c>
+      <c r="D1860" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:4">
+      <c r="A1861" t="s">
+        <v>3703</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>3704</v>
+      </c>
+      <c r="D1861" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:4">
+      <c r="A1862" t="s">
+        <v>3705</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>3268</v>
+      </c>
+      <c r="D1862" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:4">
+      <c r="A1863" t="s">
+        <v>3706</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D1863" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5593" uniqueCount="3708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5596" uniqueCount="3710">
   <si>
     <t>code</t>
   </si>
@@ -11129,6 +11129,12 @@
   </si>
   <si>
     <t>The Pirbright Institute</t>
+  </si>
+  <si>
+    <t>SE-ON-802002-3209</t>
+  </si>
+  <si>
+    <t>SMC-Faith in Development</t>
   </si>
   <si>
     <t>ET-ERCA-0056106666</t>
@@ -11469,7 +11475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1863"/>
+  <dimension ref="A1:G1864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -31960,7 +31966,7 @@
         <v>3705</v>
       </c>
       <c r="B1862" t="s">
-        <v>3268</v>
+        <v>3706</v>
       </c>
       <c r="D1862" t="s">
         <v>9</v>
@@ -31968,12 +31974,23 @@
     </row>
     <row r="1863" spans="1:4">
       <c r="A1863" t="s">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="B1863" t="s">
-        <v>3707</v>
+        <v>3268</v>
       </c>
       <c r="D1863" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:4">
+      <c r="A1864" t="s">
+        <v>3708</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D1864" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5596" uniqueCount="3710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5617" uniqueCount="3724">
   <si>
     <t>code</t>
   </si>
@@ -2944,6 +2944,12 @@
     <t>Liverpool School of Tropical Medicine</t>
   </si>
   <si>
+    <t>GB-COH-RC000710</t>
+  </si>
+  <si>
+    <t>Queen Mary University of London</t>
+  </si>
+  <si>
     <t>KE-NCB-200201282375</t>
   </si>
   <si>
@@ -9991,6 +9997,12 @@
     <t>International Foundation for Electoral Systems</t>
   </si>
   <si>
+    <t>GB-COH-46049</t>
+  </si>
+  <si>
+    <t>test dave</t>
+  </si>
+  <si>
     <t>KE-KRA-P052007235U</t>
   </si>
   <si>
@@ -10327,6 +10339,12 @@
     <t>AmplifyChange</t>
   </si>
   <si>
+    <t>YE-MOPIC-0036</t>
+  </si>
+  <si>
+    <t>Partners Yemen</t>
+  </si>
+  <si>
     <t>SZ-CIT-201710132021804</t>
   </si>
   <si>
@@ -11071,6 +11089,12 @@
     <t>piermarc</t>
   </si>
   <si>
+    <t>ET-CSA-1560</t>
+  </si>
+  <si>
+    <t>Ethiopian Orthodox Church, Developement and Inter Church Aid Commssion (EOC-DICAC)</t>
+  </si>
+  <si>
     <t>KE-RCO-CPR-2014-161876</t>
   </si>
   <si>
@@ -11125,10 +11149,28 @@
     <t>Consumer society IMTD-INTERNATIONAL</t>
   </si>
   <si>
+    <t>TR-VKN-4940457659</t>
+  </si>
+  <si>
+    <t>KAMER Women's Centre Education, Production, Consultation and Solidarity Foundation</t>
+  </si>
+  <si>
     <t>GB-COH-00559784</t>
   </si>
   <si>
     <t>The Pirbright Institute</t>
+  </si>
+  <si>
+    <t>UA-EDR-38621206</t>
+  </si>
+  <si>
+    <t>Right to Protection Charitable Fund</t>
+  </si>
+  <si>
+    <t>UA-COA-44916875</t>
+  </si>
+  <si>
+    <t>СНАRITABLE ORGANIZATHION «СНАRITABLE FOUNDATHION «VERITAS SPES+ UKRAINE»</t>
   </si>
   <si>
     <t>SE-ON-802002-3209</t>
@@ -11475,7 +11517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1864"/>
+  <dimension ref="A1:G1871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -17985,7 +18027,7 @@
         <v>1172</v>
       </c>
       <c r="B591" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D591" t="s">
         <v>9</v>
@@ -17993,10 +18035,10 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B592" t="s">
         <v>1173</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1174</v>
       </c>
       <c r="D592" t="s">
         <v>9</v>
@@ -20625,7 +20667,7 @@
         <v>1651</v>
       </c>
       <c r="B831" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="D831" t="s">
         <v>9</v>
@@ -20633,10 +20675,10 @@
     </row>
     <row r="832" spans="1:4">
       <c r="A832" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B832" t="s">
         <v>1652</v>
-      </c>
-      <c r="B832" t="s">
-        <v>1653</v>
       </c>
       <c r="D832" t="s">
         <v>9</v>
@@ -21978,7 +22020,7 @@
         <v>1896</v>
       </c>
       <c r="B954" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D954" t="s">
         <v>9</v>
@@ -21986,10 +22028,10 @@
     </row>
     <row r="955" spans="1:4">
       <c r="A955" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B955" t="s">
         <v>1897</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1898</v>
       </c>
       <c r="D955" t="s">
         <v>9</v>
@@ -24882,7 +24924,7 @@
         <v>2423</v>
       </c>
       <c r="B1218" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="D1218" t="s">
         <v>9</v>
@@ -24890,10 +24932,10 @@
     </row>
     <row r="1219" spans="1:4">
       <c r="A1219" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B1219" t="s">
         <v>2424</v>
-      </c>
-      <c r="B1219" t="s">
-        <v>2425</v>
       </c>
       <c r="D1219" t="s">
         <v>9</v>
@@ -25542,7 +25584,7 @@
         <v>2542</v>
       </c>
       <c r="B1278" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="D1278" t="s">
         <v>9</v>
@@ -25550,10 +25592,10 @@
     </row>
     <row r="1279" spans="1:4">
       <c r="A1279" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B1279" t="s">
         <v>2543</v>
-      </c>
-      <c r="B1279" t="s">
-        <v>2544</v>
       </c>
       <c r="D1279" t="s">
         <v>9</v>
@@ -26411,7 +26453,7 @@
         <v>2699</v>
       </c>
       <c r="B1357" t="s">
-        <v>2698</v>
+        <v>2700</v>
       </c>
       <c r="D1357" t="s">
         <v>9</v>
@@ -26419,10 +26461,10 @@
     </row>
     <row r="1358" spans="1:4">
       <c r="A1358" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B1358" t="s">
         <v>2700</v>
-      </c>
-      <c r="B1358" t="s">
-        <v>2701</v>
       </c>
       <c r="D1358" t="s">
         <v>9</v>
@@ -27533,7 +27575,7 @@
         <v>2902</v>
       </c>
       <c r="B1459" t="s">
-        <v>2901</v>
+        <v>2903</v>
       </c>
       <c r="D1459" t="s">
         <v>9</v>
@@ -27541,10 +27583,10 @@
     </row>
     <row r="1460" spans="1:4">
       <c r="A1460" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B1460" t="s">
         <v>2903</v>
-      </c>
-      <c r="B1460" t="s">
-        <v>2904</v>
       </c>
       <c r="D1460" t="s">
         <v>9</v>
@@ -29084,7 +29126,7 @@
         <v>3183</v>
       </c>
       <c r="B1600" t="s">
-        <v>2292</v>
+        <v>3184</v>
       </c>
       <c r="D1600" t="s">
         <v>9</v>
@@ -29092,10 +29134,10 @@
     </row>
     <row r="1601" spans="1:4">
       <c r="A1601" t="s">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="B1601" t="s">
-        <v>3185</v>
+        <v>2294</v>
       </c>
       <c r="D1601" t="s">
         <v>9</v>
@@ -29326,7 +29368,7 @@
         <v>3226</v>
       </c>
       <c r="B1622" t="s">
-        <v>3217</v>
+        <v>3227</v>
       </c>
       <c r="D1622" t="s">
         <v>9</v>
@@ -29334,10 +29376,10 @@
     </row>
     <row r="1623" spans="1:4">
       <c r="A1623" t="s">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="B1623" t="s">
-        <v>3228</v>
+        <v>3219</v>
       </c>
       <c r="D1623" t="s">
         <v>9</v>
@@ -31977,7 +32019,7 @@
         <v>3707</v>
       </c>
       <c r="B1863" t="s">
-        <v>3268</v>
+        <v>3708</v>
       </c>
       <c r="D1863" t="s">
         <v>9</v>
@@ -31985,12 +32027,89 @@
     </row>
     <row r="1864" spans="1:4">
       <c r="A1864" t="s">
-        <v>3708</v>
+        <v>3709</v>
       </c>
       <c r="B1864" t="s">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="D1864" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:4">
+      <c r="A1865" t="s">
+        <v>3711</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>3712</v>
+      </c>
+      <c r="D1865" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:4">
+      <c r="A1866" t="s">
+        <v>3713</v>
+      </c>
+      <c r="B1866" t="s">
+        <v>3714</v>
+      </c>
+      <c r="D1866" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:4">
+      <c r="A1867" t="s">
+        <v>3715</v>
+      </c>
+      <c r="B1867" t="s">
+        <v>3716</v>
+      </c>
+      <c r="D1867" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:4">
+      <c r="A1868" t="s">
+        <v>3717</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>3718</v>
+      </c>
+      <c r="D1868" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:4">
+      <c r="A1869" t="s">
+        <v>3719</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>3720</v>
+      </c>
+      <c r="D1869" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:4">
+      <c r="A1870" t="s">
+        <v>3721</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>3270</v>
+      </c>
+      <c r="D1870" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:4">
+      <c r="A1871" t="s">
+        <v>3722</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>3723</v>
+      </c>
+      <c r="D1871" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6328" uniqueCount="4195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6337" uniqueCount="4201">
   <si>
     <t>code</t>
   </si>
@@ -12193,6 +12193,12 @@
     <t>Rift Partners GmbH</t>
   </si>
   <si>
+    <t>TZ-NNCB-06NGO-00010000</t>
+  </si>
+  <si>
+    <t>Endeleza Wazee Kigoma (EWAKI)</t>
+  </si>
+  <si>
     <t>GB-GOV-28</t>
   </si>
   <si>
@@ -12277,6 +12283,12 @@
     <t>Partners In Health</t>
   </si>
   <si>
+    <t>US-SAM-P8V7YEC1GN34</t>
+  </si>
+  <si>
+    <t>Pangea Africa Ltd</t>
+  </si>
+  <si>
     <t>CR-RPJ-3-002-248583</t>
   </si>
   <si>
@@ -12329,6 +12341,12 @@
   </si>
   <si>
     <t>Rapid Asia Co., Ltd.</t>
+  </si>
+  <si>
+    <t>PK-VSWA-2172-2003</t>
+  </si>
+  <si>
+    <t>IDEA (Initiative for Development &amp; Empowerment Axis)</t>
   </si>
   <si>
     <t>SE-ON-802426-1664</t>
@@ -12930,7 +12948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2108"/>
+  <dimension ref="A1:G2111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -35698,7 +35716,7 @@
         <v>4117</v>
       </c>
       <c r="B2069" t="s">
-        <v>2888</v>
+        <v>4118</v>
       </c>
       <c r="D2069" t="s">
         <v>9</v>
@@ -35706,10 +35724,10 @@
     </row>
     <row r="2070" spans="1:4">
       <c r="A2070" t="s">
-        <v>4118</v>
+        <v>4119</v>
       </c>
       <c r="B2070" t="s">
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="D2070" t="s">
         <v>9</v>
@@ -35717,10 +35735,10 @@
     </row>
     <row r="2071" spans="1:4">
       <c r="A2071" t="s">
-        <v>4120</v>
+        <v>4121</v>
       </c>
       <c r="B2071" t="s">
-        <v>4121</v>
+        <v>4122</v>
       </c>
       <c r="D2071" t="s">
         <v>9</v>
@@ -35728,10 +35746,10 @@
     </row>
     <row r="2072" spans="1:4">
       <c r="A2072" t="s">
-        <v>4122</v>
+        <v>4123</v>
       </c>
       <c r="B2072" t="s">
-        <v>4123</v>
+        <v>2888</v>
       </c>
       <c r="D2072" t="s">
         <v>9</v>
@@ -36116,7 +36134,7 @@
         <v>4192</v>
       </c>
       <c r="B2107" t="s">
-        <v>3283</v>
+        <v>4193</v>
       </c>
       <c r="D2107" t="s">
         <v>9</v>
@@ -36124,12 +36142,45 @@
     </row>
     <row r="2108" spans="1:4">
       <c r="A2108" t="s">
-        <v>4193</v>
+        <v>4194</v>
       </c>
       <c r="B2108" t="s">
-        <v>4194</v>
+        <v>4195</v>
       </c>
       <c r="D2108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:4">
+      <c r="A2109" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>4197</v>
+      </c>
+      <c r="D2109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:4">
+      <c r="A2110" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:4">
+      <c r="A2111" t="s">
+        <v>4199</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>4200</v>
+      </c>
+      <c r="D2111" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6337" uniqueCount="4201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6382" uniqueCount="4231">
   <si>
     <t>code</t>
   </si>
@@ -3064,7 +3064,7 @@
     <t>FR-SIRET-77566669600015</t>
   </si>
   <si>
-    <t>SECOURS CATHOLIQUE - CARITAS FRANCE</t>
+    <t>Secours Catholique - Caritas France</t>
   </si>
   <si>
     <t>GB-CHC-1062638</t>
@@ -6079,7 +6079,7 @@
     <t>NL-KVK-27367015</t>
   </si>
   <si>
-    <t>Netherlands Organisation for Scientific Research (NWO)</t>
+    <t>Dutch Research Council (NWO)</t>
   </si>
   <si>
     <t>US-EIN-13-3377893</t>
@@ -10999,7 +10999,7 @@
     <t>XM-OCHA-HPC6052</t>
   </si>
   <si>
-    <t>Himilo Relief and Development Association (HIRDA)</t>
+    <t>Himilo Relief and Development Association （HIRDA Somalia）</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0665.649.335</t>
@@ -12223,6 +12223,18 @@
     <t>Africa Research &amp; Impact Network (ARIN)</t>
   </si>
   <si>
+    <t>IN-MHA-231660448</t>
+  </si>
+  <si>
+    <t>CENTRE FOR CHRONIC DISEASE CONTROL</t>
+  </si>
+  <si>
+    <t>TG-NIF-1000047187</t>
+  </si>
+  <si>
+    <t>Women in Law and Development in Africa-Afrique de l’Ouest (WiLDAF-AO)</t>
+  </si>
+  <si>
     <t>CH-FDJP-CHE365512867</t>
   </si>
   <si>
@@ -12247,6 +12259,54 @@
     <t>ADRA Sweden</t>
   </si>
   <si>
+    <t>GB-COH-07921860</t>
+  </si>
+  <si>
+    <t>Institutional Investors Group on Climate Change</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-100493543</t>
+  </si>
+  <si>
+    <t>Associaçao de Protecao do Idosos de Tete</t>
+  </si>
+  <si>
+    <t>GB-COH-12075030</t>
+  </si>
+  <si>
+    <t>Impact Knowledge Limited T/A Impact Capital Africa</t>
+  </si>
+  <si>
+    <t>GB-CHC-1111719</t>
+  </si>
+  <si>
+    <t>Anglo American Foundation</t>
+  </si>
+  <si>
+    <t>TZ-NNCB-00NGO00009862</t>
+  </si>
+  <si>
+    <t>Mtandao wa vikundi vya wakulima na wafugaji Nyancha</t>
+  </si>
+  <si>
+    <t>UA-EDR-45583070</t>
+  </si>
+  <si>
+    <t>VRUNA</t>
+  </si>
+  <si>
+    <t>XI-ROR-01ej9dk98</t>
+  </si>
+  <si>
+    <t>University of Melbourne</t>
+  </si>
+  <si>
+    <t>TH-MOI-KhorThor3005</t>
+  </si>
+  <si>
+    <t>Thai Lawyers for Human Rights</t>
+  </si>
+  <si>
     <t>SE-ON-252002-6135</t>
   </si>
   <si>
@@ -12287,6 +12347,36 @@
   </si>
   <si>
     <t>Pangea Africa Ltd</t>
+  </si>
+  <si>
+    <t>ZA-CIP-2025-956558-08</t>
+  </si>
+  <si>
+    <t>Impact Finance Facility NPC</t>
+  </si>
+  <si>
+    <t>ZA-CIT-9063151162</t>
+  </si>
+  <si>
+    <t>University of KwaZulu-Natal</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-821-B</t>
+  </si>
+  <si>
+    <t>Diocese dos Libombos - ASA</t>
+  </si>
+  <si>
+    <t>BR-CNPJ-01567601-0001-43</t>
+  </si>
+  <si>
+    <t>Universidade Federal de Goiás</t>
+  </si>
+  <si>
+    <t>ET-CSA-0067</t>
+  </si>
+  <si>
+    <t>Tesfa Social &amp; Development Association</t>
   </si>
   <si>
     <t>CR-RPJ-3-002-248583</t>
@@ -12948,7 +13038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2111"/>
+  <dimension ref="A1:G2126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -35749,7 +35839,7 @@
         <v>4123</v>
       </c>
       <c r="B2072" t="s">
-        <v>2888</v>
+        <v>4124</v>
       </c>
       <c r="D2072" t="s">
         <v>9</v>
@@ -35757,10 +35847,10 @@
     </row>
     <row r="2073" spans="1:4">
       <c r="A2073" t="s">
-        <v>4124</v>
+        <v>4125</v>
       </c>
       <c r="B2073" t="s">
-        <v>4125</v>
+        <v>4126</v>
       </c>
       <c r="D2073" t="s">
         <v>9</v>
@@ -35768,10 +35858,10 @@
     </row>
     <row r="2074" spans="1:4">
       <c r="A2074" t="s">
-        <v>4126</v>
+        <v>4127</v>
       </c>
       <c r="B2074" t="s">
-        <v>4127</v>
+        <v>4128</v>
       </c>
       <c r="D2074" t="s">
         <v>9</v>
@@ -35779,10 +35869,10 @@
     </row>
     <row r="2075" spans="1:4">
       <c r="A2075" t="s">
-        <v>4128</v>
+        <v>4129</v>
       </c>
       <c r="B2075" t="s">
-        <v>4129</v>
+        <v>4130</v>
       </c>
       <c r="D2075" t="s">
         <v>9</v>
@@ -35790,10 +35880,10 @@
     </row>
     <row r="2076" spans="1:4">
       <c r="A2076" t="s">
-        <v>4130</v>
+        <v>4131</v>
       </c>
       <c r="B2076" t="s">
-        <v>4131</v>
+        <v>4132</v>
       </c>
       <c r="D2076" t="s">
         <v>9</v>
@@ -35801,10 +35891,10 @@
     </row>
     <row r="2077" spans="1:4">
       <c r="A2077" t="s">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="B2077" t="s">
-        <v>4133</v>
+        <v>4134</v>
       </c>
       <c r="D2077" t="s">
         <v>9</v>
@@ -35812,10 +35902,10 @@
     </row>
     <row r="2078" spans="1:4">
       <c r="A2078" t="s">
-        <v>4134</v>
+        <v>4135</v>
       </c>
       <c r="B2078" t="s">
-        <v>4135</v>
+        <v>4136</v>
       </c>
       <c r="D2078" t="s">
         <v>9</v>
@@ -35823,10 +35913,10 @@
     </row>
     <row r="2079" spans="1:4">
       <c r="A2079" t="s">
-        <v>4136</v>
+        <v>4137</v>
       </c>
       <c r="B2079" t="s">
-        <v>4137</v>
+        <v>4138</v>
       </c>
       <c r="D2079" t="s">
         <v>9</v>
@@ -35834,10 +35924,10 @@
     </row>
     <row r="2080" spans="1:4">
       <c r="A2080" t="s">
-        <v>4138</v>
+        <v>4139</v>
       </c>
       <c r="B2080" t="s">
-        <v>4139</v>
+        <v>4140</v>
       </c>
       <c r="D2080" t="s">
         <v>9</v>
@@ -35845,10 +35935,10 @@
     </row>
     <row r="2081" spans="1:4">
       <c r="A2081" t="s">
-        <v>4140</v>
+        <v>4141</v>
       </c>
       <c r="B2081" t="s">
-        <v>4141</v>
+        <v>4142</v>
       </c>
       <c r="D2081" t="s">
         <v>9</v>
@@ -35856,10 +35946,10 @@
     </row>
     <row r="2082" spans="1:4">
       <c r="A2082" t="s">
-        <v>4142</v>
+        <v>4143</v>
       </c>
       <c r="B2082" t="s">
-        <v>4143</v>
+        <v>4144</v>
       </c>
       <c r="D2082" t="s">
         <v>9</v>
@@ -35867,10 +35957,10 @@
     </row>
     <row r="2083" spans="1:4">
       <c r="A2083" t="s">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="B2083" t="s">
-        <v>4145</v>
+        <v>4146</v>
       </c>
       <c r="D2083" t="s">
         <v>9</v>
@@ -35878,10 +35968,10 @@
     </row>
     <row r="2084" spans="1:4">
       <c r="A2084" t="s">
-        <v>4146</v>
+        <v>4147</v>
       </c>
       <c r="B2084" t="s">
-        <v>4147</v>
+        <v>4148</v>
       </c>
       <c r="D2084" t="s">
         <v>9</v>
@@ -35889,10 +35979,10 @@
     </row>
     <row r="2085" spans="1:4">
       <c r="A2085" t="s">
-        <v>4148</v>
+        <v>4149</v>
       </c>
       <c r="B2085" t="s">
-        <v>4149</v>
+        <v>4150</v>
       </c>
       <c r="D2085" t="s">
         <v>9</v>
@@ -35900,10 +35990,10 @@
     </row>
     <row r="2086" spans="1:4">
       <c r="A2086" t="s">
-        <v>4150</v>
+        <v>4151</v>
       </c>
       <c r="B2086" t="s">
-        <v>4151</v>
+        <v>4152</v>
       </c>
       <c r="D2086" t="s">
         <v>9</v>
@@ -35911,10 +36001,10 @@
     </row>
     <row r="2087" spans="1:4">
       <c r="A2087" t="s">
-        <v>4152</v>
+        <v>4153</v>
       </c>
       <c r="B2087" t="s">
-        <v>4153</v>
+        <v>2888</v>
       </c>
       <c r="D2087" t="s">
         <v>9</v>
@@ -36167,7 +36257,7 @@
         <v>4198</v>
       </c>
       <c r="B2110" t="s">
-        <v>3283</v>
+        <v>4199</v>
       </c>
       <c r="D2110" t="s">
         <v>9</v>
@@ -36175,12 +36265,177 @@
     </row>
     <row r="2111" spans="1:4">
       <c r="A2111" t="s">
-        <v>4199</v>
+        <v>4200</v>
       </c>
       <c r="B2111" t="s">
-        <v>4200</v>
+        <v>4201</v>
       </c>
       <c r="D2111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:4">
+      <c r="A2112" t="s">
+        <v>4202</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>4203</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:4">
+      <c r="A2113" t="s">
+        <v>4204</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>4205</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:4">
+      <c r="A2114" t="s">
+        <v>4206</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>4207</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:4">
+      <c r="A2115" t="s">
+        <v>4208</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>4209</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:4">
+      <c r="A2116" t="s">
+        <v>4210</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:4">
+      <c r="A2117" t="s">
+        <v>4212</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>4213</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:4">
+      <c r="A2118" t="s">
+        <v>4214</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>4215</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:4">
+      <c r="A2119" t="s">
+        <v>4216</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>4217</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:4">
+      <c r="A2120" t="s">
+        <v>4218</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>4219</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:4">
+      <c r="A2121" t="s">
+        <v>4220</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>4221</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:4">
+      <c r="A2122" t="s">
+        <v>4222</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>4223</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:4">
+      <c r="A2123" t="s">
+        <v>4224</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>4225</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:4">
+      <c r="A2124" t="s">
+        <v>4226</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>4227</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:4">
+      <c r="A2125" t="s">
+        <v>4228</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:4">
+      <c r="A2126" t="s">
+        <v>4229</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>4230</v>
+      </c>
+      <c r="D2126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6382" uniqueCount="4231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6388" uniqueCount="4235">
   <si>
     <t>code</t>
   </si>
@@ -12500,6 +12500,18 @@
   </si>
   <si>
     <t>Worlds Childrens Prize Foundation</t>
+  </si>
+  <si>
+    <t>GB-COH-954616</t>
+  </si>
+  <si>
+    <t>Institute for Fiscal Studies</t>
+  </si>
+  <si>
+    <t>PH-SEC-0000186387</t>
+  </si>
+  <si>
+    <t>Caucus of Development NGO Networks Inc.</t>
   </si>
   <si>
     <t>PH-SEC-AN96001837</t>
@@ -13038,7 +13050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2126"/>
+  <dimension ref="A1:G2128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -36422,7 +36434,7 @@
         <v>4228</v>
       </c>
       <c r="B2125" t="s">
-        <v>3283</v>
+        <v>4229</v>
       </c>
       <c r="D2125" t="s">
         <v>9</v>
@@ -36430,12 +36442,34 @@
     </row>
     <row r="2126" spans="1:4">
       <c r="A2126" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
       <c r="B2126" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
       <c r="D2126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:4">
+      <c r="A2127" t="s">
+        <v>4232</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:4">
+      <c r="A2128" t="s">
+        <v>4233</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>4234</v>
+      </c>
+      <c r="D2128" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6388" uniqueCount="4235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6412" uniqueCount="4251">
   <si>
     <t>code</t>
   </si>
@@ -12508,6 +12508,18 @@
     <t>Institute for Fiscal Studies</t>
   </si>
   <si>
+    <t>MM-MHA-0004-1951</t>
+  </si>
+  <si>
+    <t>Myanmar Baptist Churches Union</t>
+  </si>
+  <si>
+    <t>CR-RPJ-300304509309</t>
+  </si>
+  <si>
+    <t>Centro Agronómico Tropical de Investigación y Enseñanza-CATIE</t>
+  </si>
+  <si>
     <t>PH-SEC-0000186387</t>
   </si>
   <si>
@@ -12532,6 +12544,30 @@
     <t>National Association For Popular Action (AMEL)</t>
   </si>
   <si>
+    <t>KE-NCB-21805120120102</t>
+  </si>
+  <si>
+    <t>Action For Sustainability Initiative</t>
+  </si>
+  <si>
+    <t>KE-NCB-218051200902226007</t>
+  </si>
+  <si>
+    <t>CENTRE FOR HUMAN RIGHTS AND POLICY STUDIES</t>
+  </si>
+  <si>
+    <t>KE-RCO-CPR-2013-112912</t>
+  </si>
+  <si>
+    <t>EED Advisory Limited</t>
+  </si>
+  <si>
+    <t>IN-MHA-231660424</t>
+  </si>
+  <si>
+    <t>Integrated Research and Action For Developement</t>
+  </si>
+  <si>
     <t>GH-TIN-V0004994299</t>
   </si>
   <si>
@@ -12542,6 +12578,18 @@
   </si>
   <si>
     <t>Sierra Leone Urban Research Centre (SLURC)</t>
+  </si>
+  <si>
+    <t>XI-ROR-05m2fqn25</t>
+  </si>
+  <si>
+    <t>Chiang Mai University</t>
+  </si>
+  <si>
+    <t>CH-FDJP-CHE-207616410</t>
+  </si>
+  <si>
+    <t>Centre on Armed Groups</t>
   </si>
   <si>
     <t>GB-CHC-1193984</t>
@@ -13050,7 +13098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2128"/>
+  <dimension ref="A1:G2136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -36456,7 +36504,7 @@
         <v>4232</v>
       </c>
       <c r="B2127" t="s">
-        <v>3283</v>
+        <v>4233</v>
       </c>
       <c r="D2127" t="s">
         <v>9</v>
@@ -36464,12 +36512,100 @@
     </row>
     <row r="2128" spans="1:4">
       <c r="A2128" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
       <c r="B2128" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
       <c r="D2128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:4">
+      <c r="A2129" t="s">
+        <v>4236</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>4237</v>
+      </c>
+      <c r="D2129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:4">
+      <c r="A2130" t="s">
+        <v>4238</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>4239</v>
+      </c>
+      <c r="D2130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:4">
+      <c r="A2131" t="s">
+        <v>4240</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>4241</v>
+      </c>
+      <c r="D2131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:4">
+      <c r="A2132" t="s">
+        <v>4242</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>4243</v>
+      </c>
+      <c r="D2132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:4">
+      <c r="A2133" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>4245</v>
+      </c>
+      <c r="D2133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:4">
+      <c r="A2134" t="s">
+        <v>4246</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>4247</v>
+      </c>
+      <c r="D2134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:4">
+      <c r="A2135" t="s">
+        <v>4248</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:4">
+      <c r="A2136" t="s">
+        <v>4249</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>4250</v>
+      </c>
+      <c r="D2136" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6412" uniqueCount="4251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6415" uniqueCount="4253">
   <si>
     <t>code</t>
   </si>
@@ -2080,7 +2080,7 @@
     <t>NL-KVK-30285304</t>
   </si>
   <si>
-    <t>Stichting Humana</t>
+    <t>Sympany+</t>
   </si>
   <si>
     <t>GB-CHC-1148404</t>
@@ -12584,6 +12584,12 @@
   </si>
   <si>
     <t>Chiang Mai University</t>
+  </si>
+  <si>
+    <t>GB-UKPRN-10004180</t>
+  </si>
+  <si>
+    <t>Manchester Metropolitan University</t>
   </si>
   <si>
     <t>CH-FDJP-CHE-207616410</t>
@@ -13098,7 +13104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2136"/>
+  <dimension ref="A1:G2137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -36592,7 +36598,7 @@
         <v>4248</v>
       </c>
       <c r="B2135" t="s">
-        <v>3283</v>
+        <v>4249</v>
       </c>
       <c r="D2135" t="s">
         <v>9</v>
@@ -36600,12 +36606,23 @@
     </row>
     <row r="2136" spans="1:4">
       <c r="A2136" t="s">
-        <v>4249</v>
+        <v>4250</v>
       </c>
       <c r="B2136" t="s">
-        <v>4250</v>
+        <v>3283</v>
       </c>
       <c r="D2136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:4">
+      <c r="A2137" t="s">
+        <v>4251</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>4252</v>
+      </c>
+      <c r="D2137" t="s">
         <v>9</v>
       </c>
     </row>
